--- a/results/evaluation/gold_relevance.xlsx
+++ b/results/evaluation/gold_relevance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MinhChau\VSCode\python\System_Sematic_Search_Truyen\results\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B315E87-6A7E-4597-8BF1-58276AB824DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5A659B2-50D2-4981-983B-DFC91F18ABCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18448" uniqueCount="1336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18852" uniqueCount="1342">
   <si>
     <t>query_id</t>
   </si>
@@ -4047,6 +4047,24 @@
   </si>
   <si>
     <t>phù hợp 1 phần</t>
+  </si>
+  <si>
+    <t>trái phía</t>
+  </si>
+  <si>
+    <t>des có ít phù hợp</t>
+  </si>
+  <si>
+    <t>des phù hợp 1 phần</t>
+  </si>
+  <si>
+    <t>des phù hợp 1 ít</t>
+  </si>
+  <si>
+    <t>trạng thái lệnh xí</t>
+  </si>
+  <si>
+    <t>vi phạm quy tắc</t>
   </si>
 </sst>
 </file>
@@ -4376,8 +4394,8 @@
   <dimension ref="A1:S1814"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="42.77734375" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" customWidth="1"/>
+    <col min="2" max="2" width="49.44140625" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
     <col min="4" max="4" width="0.44140625" customWidth="1"/>
     <col min="5" max="5" width="74.6640625" customWidth="1"/>
     <col min="6" max="6" width="71.5546875" customWidth="1"/>
@@ -22419,7 +22437,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="361" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>729</v>
       </c>
@@ -22469,7 +22487,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="362" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>729</v>
       </c>
@@ -22519,7 +22537,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="363" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>729</v>
       </c>
@@ -22569,7 +22587,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="364" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>729</v>
       </c>
@@ -22619,7 +22637,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="365" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>729</v>
       </c>
@@ -22669,7 +22687,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="366" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>729</v>
       </c>
@@ -22719,7 +22737,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="367" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
         <v>729</v>
       </c>
@@ -22769,7 +22787,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="368" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
         <v>729</v>
       </c>
@@ -22819,7 +22837,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="369" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>729</v>
       </c>
@@ -22869,7 +22887,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="370" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>729</v>
       </c>
@@ -22919,7 +22937,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="371" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>729</v>
       </c>
@@ -22969,7 +22987,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="372" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>729</v>
       </c>
@@ -23019,7 +23037,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="373" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>729</v>
       </c>
@@ -23069,7 +23087,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="374" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>729</v>
       </c>
@@ -23119,7 +23137,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="375" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>729</v>
       </c>
@@ -23169,7 +23187,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="376" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>729</v>
       </c>
@@ -23219,7 +23237,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="377" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>729</v>
       </c>
@@ -23269,7 +23287,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="378" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>729</v>
       </c>
@@ -23319,7 +23337,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="379" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>729</v>
       </c>
@@ -23369,7 +23387,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="380" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>729</v>
       </c>
@@ -23462,6 +23480,12 @@
       <c r="P381" t="s">
         <v>33</v>
       </c>
+      <c r="Q381">
+        <v>1</v>
+      </c>
+      <c r="S381" t="s">
+        <v>1335</v>
+      </c>
     </row>
     <row r="382" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A382" t="s">
@@ -23506,6 +23530,12 @@
       <c r="P382" t="s">
         <v>38</v>
       </c>
+      <c r="Q382">
+        <v>1</v>
+      </c>
+      <c r="S382" t="s">
+        <v>1335</v>
+      </c>
     </row>
     <row r="383" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
@@ -23550,6 +23580,12 @@
       <c r="P383" t="s">
         <v>38</v>
       </c>
+      <c r="Q383">
+        <v>0</v>
+      </c>
+      <c r="S383" t="s">
+        <v>1336</v>
+      </c>
     </row>
     <row r="384" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
@@ -23594,8 +23630,14 @@
       <c r="P384" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="385" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q384">
+        <v>0</v>
+      </c>
+      <c r="S384" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="385" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>744</v>
       </c>
@@ -23638,8 +23680,14 @@
       <c r="P385" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="386" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q385">
+        <v>2</v>
+      </c>
+      <c r="S385" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="386" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>744</v>
       </c>
@@ -23682,8 +23730,14 @@
       <c r="P386" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="387" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q386">
+        <v>0</v>
+      </c>
+      <c r="S386" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="387" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>744</v>
       </c>
@@ -23726,8 +23780,14 @@
       <c r="P387" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="388" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q387">
+        <v>2</v>
+      </c>
+      <c r="S387" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="388" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>744</v>
       </c>
@@ -23770,8 +23830,14 @@
       <c r="P388" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="389" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q388">
+        <v>2</v>
+      </c>
+      <c r="S388" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="389" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>744</v>
       </c>
@@ -23814,8 +23880,14 @@
       <c r="P389" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="390" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q389">
+        <v>2</v>
+      </c>
+      <c r="S389" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="390" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>744</v>
       </c>
@@ -23858,8 +23930,14 @@
       <c r="P390" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="391" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q390">
+        <v>2</v>
+      </c>
+      <c r="S390" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="391" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>744</v>
       </c>
@@ -23902,8 +23980,14 @@
       <c r="P391" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="392" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q391">
+        <v>2</v>
+      </c>
+      <c r="S391" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="392" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>744</v>
       </c>
@@ -23952,8 +24036,14 @@
       <c r="P392" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="393" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q392">
+        <v>2</v>
+      </c>
+      <c r="S392" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="393" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>744</v>
       </c>
@@ -23996,8 +24086,14 @@
       <c r="P393" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="394" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q393">
+        <v>2</v>
+      </c>
+      <c r="S393" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="394" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>744</v>
       </c>
@@ -24040,8 +24136,14 @@
       <c r="P394" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="395" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q394">
+        <v>2</v>
+      </c>
+      <c r="S394" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="395" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>744</v>
       </c>
@@ -24084,8 +24186,14 @@
       <c r="P395" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="396" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q395">
+        <v>0</v>
+      </c>
+      <c r="S395" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="396" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A396" t="s">
         <v>744</v>
       </c>
@@ -24128,8 +24236,14 @@
       <c r="P396" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="397" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q396">
+        <v>2</v>
+      </c>
+      <c r="S396" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="397" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>744</v>
       </c>
@@ -24172,8 +24286,14 @@
       <c r="P397" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="398" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q397">
+        <v>1</v>
+      </c>
+      <c r="S397" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="398" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>744</v>
       </c>
@@ -24216,8 +24336,14 @@
       <c r="P398" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="399" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q398">
+        <v>1</v>
+      </c>
+      <c r="S398" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="399" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>744</v>
       </c>
@@ -24260,8 +24386,14 @@
       <c r="P399" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="400" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q399">
+        <v>2</v>
+      </c>
+      <c r="S399" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="400" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>756</v>
       </c>
@@ -24304,8 +24436,14 @@
       <c r="P400" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="401" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q400">
+        <v>2</v>
+      </c>
+      <c r="S400" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="401" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>756</v>
       </c>
@@ -24348,8 +24486,14 @@
       <c r="P401" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="402" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q401">
+        <v>2</v>
+      </c>
+      <c r="S401" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="402" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>756</v>
       </c>
@@ -24398,8 +24542,14 @@
       <c r="P402" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="403" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q402">
+        <v>2</v>
+      </c>
+      <c r="S402" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="403" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>756</v>
       </c>
@@ -24442,8 +24592,14 @@
       <c r="P403" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="404" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q403">
+        <v>2</v>
+      </c>
+      <c r="S403" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="404" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>756</v>
       </c>
@@ -24486,8 +24642,14 @@
       <c r="P404" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="405" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q404">
+        <v>2</v>
+      </c>
+      <c r="S404" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="405" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>756</v>
       </c>
@@ -24530,8 +24692,14 @@
       <c r="P405" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="406" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q405">
+        <v>1</v>
+      </c>
+      <c r="S405" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="406" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>756</v>
       </c>
@@ -24574,8 +24742,14 @@
       <c r="P406" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="407" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q406">
+        <v>1</v>
+      </c>
+      <c r="S406" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="407" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>756</v>
       </c>
@@ -24618,8 +24792,14 @@
       <c r="P407" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="408" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q407">
+        <v>1</v>
+      </c>
+      <c r="S407" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="408" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>756</v>
       </c>
@@ -24662,8 +24842,14 @@
       <c r="P408" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="409" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q408">
+        <v>0</v>
+      </c>
+      <c r="S408" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="409" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A409" t="s">
         <v>756</v>
       </c>
@@ -24706,8 +24892,14 @@
       <c r="P409" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="410" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q409">
+        <v>2</v>
+      </c>
+      <c r="S409" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="410" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>756</v>
       </c>
@@ -24750,8 +24942,14 @@
       <c r="P410" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="411" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q410">
+        <v>0</v>
+      </c>
+      <c r="S410" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="411" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>756</v>
       </c>
@@ -24794,8 +24992,14 @@
       <c r="P411" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="412" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q411">
+        <v>1</v>
+      </c>
+      <c r="S411" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="412" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>756</v>
       </c>
@@ -24838,8 +25042,14 @@
       <c r="P412" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="413" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q412">
+        <v>1</v>
+      </c>
+      <c r="S412" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="413" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>756</v>
       </c>
@@ -24882,8 +25092,14 @@
       <c r="P413" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="414" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q413">
+        <v>1</v>
+      </c>
+      <c r="S413" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="414" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>756</v>
       </c>
@@ -24926,8 +25142,14 @@
       <c r="P414" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="415" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q414">
+        <v>0</v>
+      </c>
+      <c r="S414" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="415" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>756</v>
       </c>
@@ -24970,8 +25192,14 @@
       <c r="P415" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="416" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q415">
+        <v>0</v>
+      </c>
+      <c r="S415" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="416" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>756</v>
       </c>
@@ -25014,8 +25242,14 @@
       <c r="P416" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="417" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q416">
+        <v>0</v>
+      </c>
+      <c r="S416" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="417" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>756</v>
       </c>
@@ -25058,8 +25292,14 @@
       <c r="P417" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="418" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q417">
+        <v>2</v>
+      </c>
+      <c r="S417" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="418" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>756</v>
       </c>
@@ -25102,8 +25342,14 @@
       <c r="P418" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="419" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q418">
+        <v>2</v>
+      </c>
+      <c r="S418" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="419" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>762</v>
       </c>
@@ -25152,8 +25398,14 @@
       <c r="P419" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="420" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q419">
+        <v>1</v>
+      </c>
+      <c r="S419" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="420" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>762</v>
       </c>
@@ -25196,8 +25448,14 @@
       <c r="P420" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="421" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q420">
+        <v>1</v>
+      </c>
+      <c r="S420" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="421" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>762</v>
       </c>
@@ -25240,8 +25498,14 @@
       <c r="P421" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="422" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q421">
+        <v>0</v>
+      </c>
+      <c r="S421" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="422" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>762</v>
       </c>
@@ -25284,8 +25548,14 @@
       <c r="P422" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="423" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q422">
+        <v>2</v>
+      </c>
+      <c r="S422" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="423" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>762</v>
       </c>
@@ -25328,8 +25598,14 @@
       <c r="P423" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="424" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q423">
+        <v>2</v>
+      </c>
+      <c r="S423" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="424" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>762</v>
       </c>
@@ -25372,8 +25648,14 @@
       <c r="P424" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="425" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q424">
+        <v>0</v>
+      </c>
+      <c r="S424" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="425" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>762</v>
       </c>
@@ -25416,8 +25698,14 @@
       <c r="P425" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="426" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q425">
+        <v>0</v>
+      </c>
+      <c r="S425" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="426" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>762</v>
       </c>
@@ -25460,8 +25748,14 @@
       <c r="P426" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="427" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q426">
+        <v>2</v>
+      </c>
+      <c r="S426" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="427" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>762</v>
       </c>
@@ -25504,8 +25798,14 @@
       <c r="P427" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="428" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q427">
+        <v>1</v>
+      </c>
+      <c r="S427" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="428" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>762</v>
       </c>
@@ -25548,8 +25848,14 @@
       <c r="P428" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="429" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q428">
+        <v>2</v>
+      </c>
+      <c r="S428" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="429" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>762</v>
       </c>
@@ -25592,8 +25898,14 @@
       <c r="P429" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="430" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q429">
+        <v>1</v>
+      </c>
+      <c r="S429" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="430" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>762</v>
       </c>
@@ -25636,8 +25948,14 @@
       <c r="P430" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="431" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q430">
+        <v>1</v>
+      </c>
+      <c r="S430" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="431" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>762</v>
       </c>
@@ -25680,8 +25998,14 @@
       <c r="P431" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="432" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q431">
+        <v>0</v>
+      </c>
+      <c r="S431" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="432" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>762</v>
       </c>
@@ -25724,8 +26048,14 @@
       <c r="P432" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="433" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q432">
+        <v>1</v>
+      </c>
+      <c r="S432" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="433" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>762</v>
       </c>
@@ -25768,8 +26098,14 @@
       <c r="P433" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="434" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q433">
+        <v>1</v>
+      </c>
+      <c r="S433" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="434" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>762</v>
       </c>
@@ -25812,8 +26148,14 @@
       <c r="P434" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="435" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q434">
+        <v>0</v>
+      </c>
+      <c r="S434" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="435" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>762</v>
       </c>
@@ -25856,8 +26198,14 @@
       <c r="P435" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="436" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q435">
+        <v>1</v>
+      </c>
+      <c r="S435" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="436" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>762</v>
       </c>
@@ -25900,8 +26248,14 @@
       <c r="P436" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="437" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q436">
+        <v>2</v>
+      </c>
+      <c r="S436" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="437" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>762</v>
       </c>
@@ -25944,8 +26298,14 @@
       <c r="P437" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="438" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q437">
+        <v>0</v>
+      </c>
+      <c r="S437" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="438" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>775</v>
       </c>
@@ -25988,8 +26348,14 @@
       <c r="P438" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="439" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q438">
+        <v>2</v>
+      </c>
+      <c r="S438" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="439" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>775</v>
       </c>
@@ -26038,8 +26404,14 @@
       <c r="P439" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="440" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q439">
+        <v>1</v>
+      </c>
+      <c r="S439" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="440" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>775</v>
       </c>
@@ -26082,8 +26454,14 @@
       <c r="P440" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="441" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q440">
+        <v>0</v>
+      </c>
+      <c r="S440" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="441" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>775</v>
       </c>
@@ -26126,8 +26504,14 @@
       <c r="P441" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="442" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q441">
+        <v>2</v>
+      </c>
+      <c r="S441" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="442" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>775</v>
       </c>
@@ -26170,8 +26554,14 @@
       <c r="P442" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="443" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q442">
+        <v>1</v>
+      </c>
+      <c r="S442" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="443" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>775</v>
       </c>
@@ -26214,8 +26604,14 @@
       <c r="P443" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="444" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q443">
+        <v>0</v>
+      </c>
+      <c r="S443" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="444" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>775</v>
       </c>
@@ -26258,8 +26654,14 @@
       <c r="P444" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="445" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q444">
+        <v>2</v>
+      </c>
+      <c r="S444" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="445" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>775</v>
       </c>
@@ -26302,8 +26704,14 @@
       <c r="P445" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="446" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q445">
+        <v>0</v>
+      </c>
+      <c r="S445" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="446" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>775</v>
       </c>
@@ -26346,8 +26754,14 @@
       <c r="P446" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="447" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q446">
+        <v>1</v>
+      </c>
+      <c r="S446" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="447" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>775</v>
       </c>
@@ -26390,8 +26804,14 @@
       <c r="P447" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="448" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q447">
+        <v>0</v>
+      </c>
+      <c r="S447" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="448" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>775</v>
       </c>
@@ -26440,8 +26860,14 @@
       <c r="P448" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="449" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q448">
+        <v>1</v>
+      </c>
+      <c r="S448" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="449" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>775</v>
       </c>
@@ -26484,8 +26910,14 @@
       <c r="P449" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="450" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q449">
+        <v>2</v>
+      </c>
+      <c r="S449" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="450" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>775</v>
       </c>
@@ -26528,8 +26960,14 @@
       <c r="P450" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="451" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q450">
+        <v>1</v>
+      </c>
+      <c r="S450" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="451" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>775</v>
       </c>
@@ -26572,8 +27010,14 @@
       <c r="P451" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="452" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q451">
+        <v>1</v>
+      </c>
+      <c r="S451" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="452" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>775</v>
       </c>
@@ -26616,8 +27060,14 @@
       <c r="P452" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="453" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q452">
+        <v>0</v>
+      </c>
+      <c r="S452" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="453" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>775</v>
       </c>
@@ -26660,8 +27110,14 @@
       <c r="P453" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="454" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q453">
+        <v>0</v>
+      </c>
+      <c r="S453" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="454" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>775</v>
       </c>
@@ -26704,8 +27160,14 @@
       <c r="P454" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="455" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q454">
+        <v>2</v>
+      </c>
+      <c r="S454" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="455" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>775</v>
       </c>
@@ -26748,8 +27210,14 @@
       <c r="P455" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="456" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q455">
+        <v>2</v>
+      </c>
+      <c r="S455" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="456" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>781</v>
       </c>
@@ -26792,8 +27260,14 @@
       <c r="P456" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="457" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q456">
+        <v>2</v>
+      </c>
+      <c r="S456" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="457" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>781</v>
       </c>
@@ -26836,8 +27310,14 @@
       <c r="P457" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="458" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q457">
+        <v>0</v>
+      </c>
+      <c r="S457" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="458" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A458" t="s">
         <v>781</v>
       </c>
@@ -26880,8 +27360,14 @@
       <c r="P458" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="459" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q458">
+        <v>2</v>
+      </c>
+      <c r="S458" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="459" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>781</v>
       </c>
@@ -26924,8 +27410,14 @@
       <c r="P459" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="460" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q459">
+        <v>1</v>
+      </c>
+      <c r="S459" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="460" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>781</v>
       </c>
@@ -26968,8 +27460,14 @@
       <c r="P460" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="461" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q460">
+        <v>2</v>
+      </c>
+      <c r="S460" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="461" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>781</v>
       </c>
@@ -27012,8 +27510,14 @@
       <c r="P461" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="462" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q461">
+        <v>2</v>
+      </c>
+      <c r="S461" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="462" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>781</v>
       </c>
@@ -27056,8 +27560,14 @@
       <c r="P462" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="463" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q462">
+        <v>2</v>
+      </c>
+      <c r="S462" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="463" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>781</v>
       </c>
@@ -27100,8 +27610,14 @@
       <c r="P463" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="464" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q463">
+        <v>2</v>
+      </c>
+      <c r="S463" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="464" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>781</v>
       </c>
@@ -27144,8 +27660,14 @@
       <c r="P464" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="465" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q464">
+        <v>2</v>
+      </c>
+      <c r="S464" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="465" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>781</v>
       </c>
@@ -27188,8 +27710,14 @@
       <c r="P465" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="466" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q465">
+        <v>1</v>
+      </c>
+      <c r="S465" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="466" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>781</v>
       </c>
@@ -27232,8 +27760,14 @@
       <c r="P466" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="467" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q466">
+        <v>2</v>
+      </c>
+      <c r="S466" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="467" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>781</v>
       </c>
@@ -27276,8 +27810,14 @@
       <c r="P467" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="468" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q467">
+        <v>2</v>
+      </c>
+      <c r="S467" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="468" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>781</v>
       </c>
@@ -27320,8 +27860,14 @@
       <c r="P468" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="469" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q468">
+        <v>2</v>
+      </c>
+      <c r="S468" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="469" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A469" t="s">
         <v>781</v>
       </c>
@@ -27364,8 +27910,14 @@
       <c r="P469" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="470" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q469">
+        <v>2</v>
+      </c>
+      <c r="S469" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="470" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A470" t="s">
         <v>781</v>
       </c>
@@ -27408,8 +27960,14 @@
       <c r="P470" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="471" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q470">
+        <v>0</v>
+      </c>
+      <c r="S470" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="471" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>781</v>
       </c>
@@ -27452,8 +28010,14 @@
       <c r="P471" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="472" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q471">
+        <v>0</v>
+      </c>
+      <c r="S471" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="472" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>781</v>
       </c>
@@ -27496,8 +28060,14 @@
       <c r="P472" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="473" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q472">
+        <v>2</v>
+      </c>
+      <c r="S472" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="473" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>781</v>
       </c>
@@ -27540,8 +28110,14 @@
       <c r="P473" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="474" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q473">
+        <v>2</v>
+      </c>
+      <c r="S473" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="474" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>781</v>
       </c>
@@ -27584,8 +28160,14 @@
       <c r="P474" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="475" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q474">
+        <v>2</v>
+      </c>
+      <c r="S474" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="475" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>781</v>
       </c>
@@ -27628,8 +28210,14 @@
       <c r="P475" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="476" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q475">
+        <v>2</v>
+      </c>
+      <c r="S475" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="476" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>791</v>
       </c>
@@ -27678,8 +28266,14 @@
       <c r="P476" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="477" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q476">
+        <v>2</v>
+      </c>
+      <c r="S476" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="477" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>791</v>
       </c>
@@ -27722,8 +28316,14 @@
       <c r="P477" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="478" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q477">
+        <v>2</v>
+      </c>
+      <c r="S477" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="478" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>791</v>
       </c>
@@ -27766,8 +28366,14 @@
       <c r="P478" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="479" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q478">
+        <v>2</v>
+      </c>
+      <c r="S478" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="479" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>791</v>
       </c>
@@ -27810,8 +28416,14 @@
       <c r="P479" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="480" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q479">
+        <v>2</v>
+      </c>
+      <c r="S479" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="480" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>791</v>
       </c>
@@ -27854,8 +28466,14 @@
       <c r="P480" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="481" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q480">
+        <v>2</v>
+      </c>
+      <c r="S480" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="481" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A481" t="s">
         <v>791</v>
       </c>
@@ -27904,8 +28522,14 @@
       <c r="P481" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="482" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q481">
+        <v>2</v>
+      </c>
+      <c r="S481" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="482" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>791</v>
       </c>
@@ -27954,8 +28578,14 @@
       <c r="P482" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="483" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q482">
+        <v>2</v>
+      </c>
+      <c r="S482" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="483" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>791</v>
       </c>
@@ -27998,8 +28628,14 @@
       <c r="P483" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="484" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q483">
+        <v>2</v>
+      </c>
+      <c r="S483" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="484" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A484" t="s">
         <v>791</v>
       </c>
@@ -28042,8 +28678,14 @@
       <c r="P484" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="485" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q484">
+        <v>2</v>
+      </c>
+      <c r="S484" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="485" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>791</v>
       </c>
@@ -28086,8 +28728,14 @@
       <c r="P485" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="486" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q485">
+        <v>0</v>
+      </c>
+      <c r="S485" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="486" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>791</v>
       </c>
@@ -28130,8 +28778,14 @@
       <c r="P486" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="487" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q486">
+        <v>0</v>
+      </c>
+      <c r="S486" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="487" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>791</v>
       </c>
@@ -28180,8 +28834,14 @@
       <c r="P487" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="488" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q487">
+        <v>1</v>
+      </c>
+      <c r="S487" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="488" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>791</v>
       </c>
@@ -28224,8 +28884,14 @@
       <c r="P488" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="489" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q488">
+        <v>2</v>
+      </c>
+      <c r="S488" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="489" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>791</v>
       </c>
@@ -28268,8 +28934,14 @@
       <c r="P489" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="490" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q489">
+        <v>2</v>
+      </c>
+      <c r="S489" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="490" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>791</v>
       </c>
@@ -28312,8 +28984,14 @@
       <c r="P490" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="491" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q490">
+        <v>2</v>
+      </c>
+      <c r="S490" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="491" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>791</v>
       </c>
@@ -28356,8 +29034,14 @@
       <c r="P491" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="492" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q491">
+        <v>2</v>
+      </c>
+      <c r="S491" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="492" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>797</v>
       </c>
@@ -28400,8 +29084,14 @@
       <c r="P492" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="493" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q492">
+        <v>2</v>
+      </c>
+      <c r="S492" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="493" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>797</v>
       </c>
@@ -28444,8 +29134,14 @@
       <c r="P493" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="494" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q493">
+        <v>2</v>
+      </c>
+      <c r="S493" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="494" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>797</v>
       </c>
@@ -28488,8 +29184,14 @@
       <c r="P494" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="495" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q494">
+        <v>2</v>
+      </c>
+      <c r="S494" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="495" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A495" t="s">
         <v>797</v>
       </c>
@@ -28532,8 +29234,14 @@
       <c r="P495" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="496" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q495">
+        <v>2</v>
+      </c>
+      <c r="S495" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="496" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>797</v>
       </c>
@@ -28576,8 +29284,14 @@
       <c r="P496" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="497" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q496">
+        <v>2</v>
+      </c>
+      <c r="S496" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="497" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>797</v>
       </c>
@@ -28620,8 +29334,14 @@
       <c r="P497" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="498" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q497">
+        <v>1</v>
+      </c>
+      <c r="S497" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="498" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>797</v>
       </c>
@@ -28664,8 +29384,14 @@
       <c r="P498" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="499" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q498">
+        <v>2</v>
+      </c>
+      <c r="S498" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="499" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>797</v>
       </c>
@@ -28708,8 +29434,14 @@
       <c r="P499" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="500" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q499">
+        <v>2</v>
+      </c>
+      <c r="S499" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="500" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>797</v>
       </c>
@@ -28752,8 +29484,14 @@
       <c r="P500" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="501" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q500">
+        <v>1</v>
+      </c>
+      <c r="S500" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="501" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>797</v>
       </c>
@@ -28796,8 +29534,14 @@
       <c r="P501" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="502" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q501">
+        <v>1</v>
+      </c>
+      <c r="S501" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="502" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>797</v>
       </c>
@@ -28840,8 +29584,14 @@
       <c r="P502" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="503" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q502">
+        <v>0</v>
+      </c>
+      <c r="S502" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="503" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>797</v>
       </c>
@@ -28884,8 +29634,14 @@
       <c r="P503" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="504" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q503">
+        <v>1</v>
+      </c>
+      <c r="S503" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="504" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>797</v>
       </c>
@@ -28928,8 +29684,14 @@
       <c r="P504" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="505" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q504">
+        <v>1</v>
+      </c>
+      <c r="S504" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="505" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>797</v>
       </c>
@@ -28972,8 +29734,14 @@
       <c r="P505" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="506" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q505">
+        <v>1</v>
+      </c>
+      <c r="S505" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="506" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>797</v>
       </c>
@@ -29016,8 +29784,14 @@
       <c r="P506" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="507" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q506">
+        <v>2</v>
+      </c>
+      <c r="S506" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="507" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>797</v>
       </c>
@@ -29060,8 +29834,14 @@
       <c r="P507" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="508" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q507">
+        <v>1</v>
+      </c>
+      <c r="S507" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="508" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>797</v>
       </c>
@@ -29104,8 +29884,14 @@
       <c r="P508" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="509" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q508">
+        <v>0</v>
+      </c>
+      <c r="S508" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="509" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>797</v>
       </c>
@@ -29148,8 +29934,14 @@
       <c r="P509" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="510" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q509">
+        <v>2</v>
+      </c>
+      <c r="S509" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="510" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>797</v>
       </c>
@@ -29192,8 +29984,14 @@
       <c r="P510" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="511" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q510">
+        <v>1</v>
+      </c>
+      <c r="S510" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="511" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>797</v>
       </c>
@@ -29236,8 +30034,14 @@
       <c r="P511" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="512" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q511">
+        <v>2</v>
+      </c>
+      <c r="S511" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="512" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>803</v>
       </c>
@@ -29286,8 +30090,14 @@
       <c r="P512" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="513" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q512">
+        <v>1</v>
+      </c>
+      <c r="S512" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="513" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>803</v>
       </c>
@@ -29330,8 +30140,14 @@
       <c r="P513" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="514" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q513">
+        <v>1</v>
+      </c>
+      <c r="S513" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="514" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>803</v>
       </c>
@@ -29374,8 +30190,14 @@
       <c r="P514" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="515" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q514">
+        <v>1</v>
+      </c>
+      <c r="S514" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="515" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>803</v>
       </c>
@@ -29418,8 +30240,14 @@
       <c r="P515" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="516" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q515">
+        <v>0</v>
+      </c>
+      <c r="S515" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="516" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>803</v>
       </c>
@@ -29462,8 +30290,14 @@
       <c r="P516" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="517" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q516">
+        <v>2</v>
+      </c>
+      <c r="S516" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="517" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A517" t="s">
         <v>803</v>
       </c>
@@ -29506,8 +30340,14 @@
       <c r="P517" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="518" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q517">
+        <v>0</v>
+      </c>
+      <c r="S517" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="518" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>803</v>
       </c>
@@ -29550,8 +30390,14 @@
       <c r="P518" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="519" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q518">
+        <v>2</v>
+      </c>
+      <c r="S518" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="519" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>803</v>
       </c>
@@ -29594,8 +30440,14 @@
       <c r="P519" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="520" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q519">
+        <v>1</v>
+      </c>
+      <c r="S519" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="520" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>803</v>
       </c>
@@ -29638,8 +30490,14 @@
       <c r="P520" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="521" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q520">
+        <v>1</v>
+      </c>
+      <c r="S520" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="521" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>803</v>
       </c>
@@ -29682,8 +30540,14 @@
       <c r="P521" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="522" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q521">
+        <v>0</v>
+      </c>
+      <c r="S521" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="522" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>803</v>
       </c>
@@ -29726,8 +30590,14 @@
       <c r="P522" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="523" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q522">
+        <v>2</v>
+      </c>
+      <c r="S522" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="523" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>803</v>
       </c>
@@ -29770,8 +30640,14 @@
       <c r="P523" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="524" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q523">
+        <v>2</v>
+      </c>
+      <c r="S523" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="524" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>803</v>
       </c>
@@ -29814,8 +30690,14 @@
       <c r="P524" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="525" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q524">
+        <v>1</v>
+      </c>
+      <c r="S524" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="525" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>803</v>
       </c>
@@ -29858,8 +30740,14 @@
       <c r="P525" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="526" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q525">
+        <v>0</v>
+      </c>
+      <c r="S525" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="526" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>803</v>
       </c>
@@ -29902,8 +30790,14 @@
       <c r="P526" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="527" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q526">
+        <v>0</v>
+      </c>
+      <c r="S526" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="527" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>803</v>
       </c>
@@ -29946,8 +30840,14 @@
       <c r="P527" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="528" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q527">
+        <v>1</v>
+      </c>
+      <c r="S527" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="528" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A528" t="s">
         <v>803</v>
       </c>
@@ -29990,8 +30890,14 @@
       <c r="P528" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="529" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q528">
+        <v>1</v>
+      </c>
+      <c r="S528" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="529" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>803</v>
       </c>
@@ -30034,8 +30940,14 @@
       <c r="P529" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="530" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q529">
+        <v>1</v>
+      </c>
+      <c r="S529" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="530" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>803</v>
       </c>
@@ -30078,8 +30990,14 @@
       <c r="P530" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="531" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q530">
+        <v>2</v>
+      </c>
+      <c r="S530" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="531" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>809</v>
       </c>
@@ -30122,8 +31040,14 @@
       <c r="P531" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="532" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q531">
+        <v>2</v>
+      </c>
+      <c r="S531" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="532" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>809</v>
       </c>
@@ -30166,8 +31090,14 @@
       <c r="P532" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="533" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q532">
+        <v>1</v>
+      </c>
+      <c r="S532" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="533" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>809</v>
       </c>
@@ -30210,8 +31140,14 @@
       <c r="P533" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="534" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q533">
+        <v>1</v>
+      </c>
+      <c r="S533" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="534" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>809</v>
       </c>
@@ -30254,8 +31190,14 @@
       <c r="P534" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="535" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q534">
+        <v>0</v>
+      </c>
+      <c r="S534" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="535" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>809</v>
       </c>
@@ -30298,8 +31240,14 @@
       <c r="P535" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="536" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q535">
+        <v>1</v>
+      </c>
+      <c r="S535" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="536" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>809</v>
       </c>
@@ -30342,8 +31290,14 @@
       <c r="P536" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="537" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q536">
+        <v>2</v>
+      </c>
+      <c r="S536" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="537" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>809</v>
       </c>
@@ -30386,8 +31340,14 @@
       <c r="P537" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="538" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q537">
+        <v>1</v>
+      </c>
+      <c r="S537" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="538" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>809</v>
       </c>
@@ -30436,8 +31396,14 @@
       <c r="P538" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="539" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q538">
+        <v>2</v>
+      </c>
+      <c r="S538" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="539" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>809</v>
       </c>
@@ -30480,8 +31446,14 @@
       <c r="P539" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="540" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q539">
+        <v>1</v>
+      </c>
+      <c r="S539" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="540" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>809</v>
       </c>
@@ -30524,8 +31496,14 @@
       <c r="P540" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="541" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q540">
+        <v>2</v>
+      </c>
+      <c r="S540" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="541" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>809</v>
       </c>
@@ -30568,8 +31546,14 @@
       <c r="P541" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="542" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q541">
+        <v>1</v>
+      </c>
+      <c r="S541" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="542" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>809</v>
       </c>
@@ -30612,8 +31596,14 @@
       <c r="P542" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="543" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q542">
+        <v>1</v>
+      </c>
+      <c r="S542" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="543" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>809</v>
       </c>
@@ -30656,8 +31646,14 @@
       <c r="P543" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="544" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q543">
+        <v>1</v>
+      </c>
+      <c r="S543" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="544" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>809</v>
       </c>
@@ -30700,8 +31696,14 @@
       <c r="P544" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="545" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q544">
+        <v>2</v>
+      </c>
+      <c r="S544" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="545" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>809</v>
       </c>
@@ -30744,8 +31746,14 @@
       <c r="P545" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="546" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q545">
+        <v>0</v>
+      </c>
+      <c r="S545" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="546" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>809</v>
       </c>
@@ -30788,8 +31796,14 @@
       <c r="P546" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="547" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q546">
+        <v>2</v>
+      </c>
+      <c r="S546" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="547" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>809</v>
       </c>
@@ -30832,8 +31846,14 @@
       <c r="P547" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="548" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q547">
+        <v>1</v>
+      </c>
+      <c r="S547" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="548" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>809</v>
       </c>
@@ -30876,8 +31896,14 @@
       <c r="P548" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="549" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q548">
+        <v>2</v>
+      </c>
+      <c r="S548" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="549" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>809</v>
       </c>
@@ -30920,8 +31946,14 @@
       <c r="P549" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="550" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q549">
+        <v>1</v>
+      </c>
+      <c r="S549" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="550" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>811</v>
       </c>
@@ -30970,8 +32002,14 @@
       <c r="P550" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="551" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q550">
+        <v>2</v>
+      </c>
+      <c r="S550" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="551" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>811</v>
       </c>
@@ -31014,8 +32052,14 @@
       <c r="P551" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="552" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q551">
+        <v>2</v>
+      </c>
+      <c r="S551" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="552" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>811</v>
       </c>
@@ -31058,8 +32102,14 @@
       <c r="P552" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="553" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q552">
+        <v>2</v>
+      </c>
+      <c r="S552" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="553" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>811</v>
       </c>
@@ -31108,8 +32158,14 @@
       <c r="P553" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="554" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q553">
+        <v>2</v>
+      </c>
+      <c r="S553" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="554" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A554" t="s">
         <v>811</v>
       </c>
@@ -31152,8 +32208,14 @@
       <c r="P554" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="555" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q554">
+        <v>2</v>
+      </c>
+      <c r="S554" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="555" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>811</v>
       </c>
@@ -31202,8 +32264,14 @@
       <c r="P555" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="556" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q555">
+        <v>2</v>
+      </c>
+      <c r="S555" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="556" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>811</v>
       </c>
@@ -31246,8 +32314,14 @@
       <c r="P556" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="557" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q556">
+        <v>0</v>
+      </c>
+      <c r="S556" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="557" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>811</v>
       </c>
@@ -31296,8 +32370,14 @@
       <c r="P557" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="558" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q557">
+        <v>1</v>
+      </c>
+      <c r="S557" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="558" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>811</v>
       </c>
@@ -31346,8 +32426,14 @@
       <c r="P558" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="559" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q558">
+        <v>2</v>
+      </c>
+      <c r="S558" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="559" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>811</v>
       </c>
@@ -31390,8 +32476,14 @@
       <c r="P559" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="560" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q559">
+        <v>1</v>
+      </c>
+      <c r="S559" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="560" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>811</v>
       </c>
@@ -31440,8 +32532,14 @@
       <c r="P560" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="561" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q560">
+        <v>2</v>
+      </c>
+      <c r="S560" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="561" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>811</v>
       </c>
@@ -31490,8 +32588,14 @@
       <c r="P561" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="562" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q561">
+        <v>2</v>
+      </c>
+      <c r="S561" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="562" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>811</v>
       </c>
@@ -31534,8 +32638,14 @@
       <c r="P562" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="563" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q562">
+        <v>1</v>
+      </c>
+      <c r="S562" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="563" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>825</v>
       </c>
@@ -31584,8 +32694,14 @@
       <c r="P563" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="564" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q563">
+        <v>1</v>
+      </c>
+      <c r="S563" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="564" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>825</v>
       </c>
@@ -31628,8 +32744,14 @@
       <c r="P564" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="565" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q564">
+        <v>1</v>
+      </c>
+      <c r="S564" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="565" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>825</v>
       </c>
@@ -31672,8 +32794,14 @@
       <c r="P565" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="566" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q565">
+        <v>1</v>
+      </c>
+      <c r="S565" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="566" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>825</v>
       </c>
@@ -31722,8 +32850,14 @@
       <c r="P566" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="567" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q566">
+        <v>2</v>
+      </c>
+      <c r="S566" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="567" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>825</v>
       </c>
@@ -31772,8 +32906,14 @@
       <c r="P567" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="568" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q567">
+        <v>2</v>
+      </c>
+      <c r="S567" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="568" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>825</v>
       </c>
@@ -31816,8 +32956,14 @@
       <c r="P568" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="569" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q568">
+        <v>1</v>
+      </c>
+      <c r="S568" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="569" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>825</v>
       </c>
@@ -31860,8 +33006,14 @@
       <c r="P569" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="570" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q569">
+        <v>2</v>
+      </c>
+      <c r="S569" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="570" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>825</v>
       </c>
@@ -31904,8 +33056,14 @@
       <c r="P570" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="571" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q570">
+        <v>1</v>
+      </c>
+      <c r="S570" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="571" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>825</v>
       </c>
@@ -31954,8 +33112,14 @@
       <c r="P571" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="572" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q571">
+        <v>2</v>
+      </c>
+      <c r="S571" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="572" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>825</v>
       </c>
@@ -31998,8 +33162,14 @@
       <c r="P572" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="573" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q572">
+        <v>1</v>
+      </c>
+      <c r="S572" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="573" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>825</v>
       </c>
@@ -32042,8 +33212,14 @@
       <c r="P573" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="574" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q573">
+        <v>2</v>
+      </c>
+      <c r="S573" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="574" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>825</v>
       </c>
@@ -32086,8 +33262,14 @@
       <c r="P574" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="575" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q574">
+        <v>2</v>
+      </c>
+      <c r="S574" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="575" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>825</v>
       </c>
@@ -32130,8 +33312,14 @@
       <c r="P575" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="576" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q575">
+        <v>2</v>
+      </c>
+      <c r="S575" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="576" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>825</v>
       </c>
@@ -32174,8 +33362,14 @@
       <c r="P576" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="577" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q576">
+        <v>1</v>
+      </c>
+      <c r="S576" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="577" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>825</v>
       </c>
@@ -32218,8 +33412,14 @@
       <c r="P577" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="578" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q577">
+        <v>2</v>
+      </c>
+      <c r="S577" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="578" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A578" t="s">
         <v>825</v>
       </c>
@@ -32262,8 +33462,14 @@
       <c r="P578" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="579" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q578">
+        <v>1</v>
+      </c>
+      <c r="S578" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="579" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>845</v>
       </c>
@@ -32312,8 +33518,14 @@
       <c r="P579" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="580" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q579">
+        <v>1</v>
+      </c>
+      <c r="S579" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="580" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>845</v>
       </c>
@@ -32356,8 +33568,14 @@
       <c r="P580" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="581" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q580">
+        <v>1</v>
+      </c>
+      <c r="S580" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="581" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>845</v>
       </c>
@@ -32406,8 +33624,14 @@
       <c r="P581" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="582" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q581">
+        <v>1</v>
+      </c>
+      <c r="S581" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="582" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>845</v>
       </c>
@@ -32456,8 +33680,14 @@
       <c r="P582" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="583" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q582">
+        <v>1</v>
+      </c>
+      <c r="S582" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="583" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>845</v>
       </c>
@@ -32506,8 +33736,14 @@
       <c r="P583" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="584" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q583">
+        <v>2</v>
+      </c>
+      <c r="S583" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="584" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>845</v>
       </c>
@@ -32550,8 +33786,14 @@
       <c r="P584" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="585" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q584">
+        <v>1</v>
+      </c>
+      <c r="S584" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="585" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>845</v>
       </c>
@@ -32594,8 +33836,14 @@
       <c r="P585" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="586" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q585">
+        <v>2</v>
+      </c>
+      <c r="S585" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="586" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>845</v>
       </c>
@@ -32638,8 +33886,14 @@
       <c r="P586" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="587" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q586">
+        <v>1</v>
+      </c>
+      <c r="S586" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="587" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>845</v>
       </c>
@@ -32682,8 +33936,14 @@
       <c r="P587" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="588" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q587">
+        <v>2</v>
+      </c>
+      <c r="S587" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="588" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>845</v>
       </c>
@@ -32726,8 +33986,14 @@
       <c r="P588" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="589" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q588">
+        <v>1</v>
+      </c>
+      <c r="S588" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="589" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>845</v>
       </c>
@@ -32770,8 +34036,14 @@
       <c r="P589" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="590" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q589">
+        <v>0</v>
+      </c>
+      <c r="S589" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="590" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A590" t="s">
         <v>845</v>
       </c>
@@ -32820,8 +34092,14 @@
       <c r="P590" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="591" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q590">
+        <v>0</v>
+      </c>
+      <c r="S590" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="591" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A591" t="s">
         <v>845</v>
       </c>
@@ -32864,8 +34142,14 @@
       <c r="P591" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="592" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q591">
+        <v>0</v>
+      </c>
+      <c r="S591" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="592" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A592" t="s">
         <v>845</v>
       </c>
@@ -32908,8 +34192,14 @@
       <c r="P592" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="593" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q592">
+        <v>1</v>
+      </c>
+      <c r="S592" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="593" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>845</v>
       </c>
@@ -32952,8 +34242,14 @@
       <c r="P593" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="594" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q593">
+        <v>0</v>
+      </c>
+      <c r="S593" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="594" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>856</v>
       </c>
@@ -32996,8 +34292,14 @@
       <c r="P594" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="595" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q594">
+        <v>0</v>
+      </c>
+      <c r="S594" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="595" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>856</v>
       </c>
@@ -33040,8 +34342,14 @@
       <c r="P595" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="596" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q595">
+        <v>1</v>
+      </c>
+      <c r="S595" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="596" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A596" t="s">
         <v>856</v>
       </c>
@@ -33090,8 +34398,14 @@
       <c r="P596" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="597" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q596">
+        <v>2</v>
+      </c>
+      <c r="S596" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="597" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>856</v>
       </c>
@@ -33134,8 +34448,14 @@
       <c r="P597" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="598" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q597">
+        <v>2</v>
+      </c>
+      <c r="S597" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="598" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>856</v>
       </c>
@@ -33178,8 +34498,14 @@
       <c r="P598" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="599" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q598">
+        <v>1</v>
+      </c>
+      <c r="S598" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="599" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>856</v>
       </c>
@@ -33222,8 +34548,14 @@
       <c r="P599" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="600" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q599">
+        <v>0</v>
+      </c>
+      <c r="S599" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="600" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>856</v>
       </c>
@@ -33266,8 +34598,14 @@
       <c r="P600" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="601" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q600">
+        <v>0</v>
+      </c>
+      <c r="S600" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="601" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>856</v>
       </c>
@@ -33310,8 +34648,14 @@
       <c r="P601" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="602" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q601">
+        <v>1</v>
+      </c>
+      <c r="S601" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="602" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A602" t="s">
         <v>856</v>
       </c>
@@ -33354,8 +34698,14 @@
       <c r="P602" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="603" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q602">
+        <v>2</v>
+      </c>
+      <c r="S602" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="603" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>856</v>
       </c>
@@ -33398,8 +34748,14 @@
       <c r="P603" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="604" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q603">
+        <v>0</v>
+      </c>
+      <c r="S603" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="604" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>856</v>
       </c>
@@ -33442,8 +34798,14 @@
       <c r="P604" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="605" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q604">
+        <v>2</v>
+      </c>
+      <c r="S604" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="605" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>856</v>
       </c>
@@ -33486,8 +34848,14 @@
       <c r="P605" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="606" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q605">
+        <v>0</v>
+      </c>
+      <c r="S605" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="606" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>856</v>
       </c>
@@ -33530,8 +34898,14 @@
       <c r="P606" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="607" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q606">
+        <v>1</v>
+      </c>
+      <c r="S606" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="607" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>856</v>
       </c>
@@ -33574,8 +34948,14 @@
       <c r="P607" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="608" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q607">
+        <v>0</v>
+      </c>
+      <c r="S607" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="608" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>856</v>
       </c>
@@ -33618,8 +34998,14 @@
       <c r="P608" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="609" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q608">
+        <v>2</v>
+      </c>
+      <c r="S608" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="609" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>856</v>
       </c>
@@ -33662,8 +35048,14 @@
       <c r="P609" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="610" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q609">
+        <v>0</v>
+      </c>
+      <c r="S609" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="610" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>856</v>
       </c>
@@ -33706,8 +35098,14 @@
       <c r="P610" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="611" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q610">
+        <v>0</v>
+      </c>
+      <c r="S610" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="611" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>856</v>
       </c>
@@ -33750,8 +35148,14 @@
       <c r="P611" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="612" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q611">
+        <v>0</v>
+      </c>
+      <c r="S611" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="612" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>856</v>
       </c>
@@ -33794,8 +35198,14 @@
       <c r="P612" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="613" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q612">
+        <v>1</v>
+      </c>
+      <c r="S612" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="613" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>874</v>
       </c>
@@ -33838,8 +35248,14 @@
       <c r="P613" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="614" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q613">
+        <v>2</v>
+      </c>
+      <c r="S613" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="614" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>874</v>
       </c>
@@ -33882,8 +35298,14 @@
       <c r="P614" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="615" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q614">
+        <v>0</v>
+      </c>
+      <c r="S614" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="615" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>874</v>
       </c>
@@ -33932,8 +35354,14 @@
       <c r="P615" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="616" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q615">
+        <v>2</v>
+      </c>
+      <c r="S615" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="616" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>874</v>
       </c>
@@ -33976,8 +35404,14 @@
       <c r="P616" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="617" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q616">
+        <v>0</v>
+      </c>
+      <c r="S616" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="617" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>874</v>
       </c>
@@ -34020,8 +35454,14 @@
       <c r="P617" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="618" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q617">
+        <v>2</v>
+      </c>
+      <c r="S617" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="618" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>874</v>
       </c>
@@ -34064,8 +35504,14 @@
       <c r="P618" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="619" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q618">
+        <v>1</v>
+      </c>
+      <c r="S618" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="619" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A619" t="s">
         <v>874</v>
       </c>
@@ -34108,8 +35554,14 @@
       <c r="P619" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="620" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q619">
+        <v>1</v>
+      </c>
+      <c r="S619" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="620" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>874</v>
       </c>
@@ -34152,8 +35604,14 @@
       <c r="P620" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="621" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q620">
+        <v>2</v>
+      </c>
+      <c r="S620" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="621" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>874</v>
       </c>
@@ -34196,8 +35654,14 @@
       <c r="P621" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="622" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q621">
+        <v>0</v>
+      </c>
+      <c r="S621" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="622" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>874</v>
       </c>
@@ -34240,8 +35704,14 @@
       <c r="P622" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="623" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q622">
+        <v>1</v>
+      </c>
+      <c r="S622" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="623" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>874</v>
       </c>
@@ -34284,8 +35754,14 @@
       <c r="P623" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="624" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q623">
+        <v>2</v>
+      </c>
+      <c r="S623" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="624" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>874</v>
       </c>
@@ -34328,8 +35804,14 @@
       <c r="P624" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="625" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q624">
+        <v>2</v>
+      </c>
+      <c r="S624" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="625" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>874</v>
       </c>
@@ -34372,8 +35854,14 @@
       <c r="P625" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="626" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q625">
+        <v>1</v>
+      </c>
+      <c r="S625" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="626" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>874</v>
       </c>
@@ -34416,8 +35904,14 @@
       <c r="P626" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="627" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q626">
+        <v>2</v>
+      </c>
+      <c r="S626" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="627" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>874</v>
       </c>
@@ -34460,8 +35954,14 @@
       <c r="P627" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="628" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q627">
+        <v>0</v>
+      </c>
+      <c r="S627" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="628" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>874</v>
       </c>
@@ -34504,8 +36004,14 @@
       <c r="P628" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="629" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q628">
+        <v>1</v>
+      </c>
+      <c r="S628" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="629" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>874</v>
       </c>
@@ -34548,8 +36054,14 @@
       <c r="P629" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="630" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q629">
+        <v>0</v>
+      </c>
+      <c r="S629" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="630" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>874</v>
       </c>
@@ -34592,8 +36104,14 @@
       <c r="P630" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="631" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q630">
+        <v>0</v>
+      </c>
+      <c r="S630" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="631" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>874</v>
       </c>
@@ -34636,8 +36154,14 @@
       <c r="P631" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="632" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q631">
+        <v>1</v>
+      </c>
+      <c r="S631" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="632" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>883</v>
       </c>
@@ -34680,8 +36204,14 @@
       <c r="P632" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="633" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q632">
+        <v>1</v>
+      </c>
+      <c r="S632" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="633" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>883</v>
       </c>
@@ -34724,8 +36254,14 @@
       <c r="P633" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="634" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q633">
+        <v>2</v>
+      </c>
+      <c r="S633" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="634" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>883</v>
       </c>
@@ -34768,8 +36304,14 @@
       <c r="P634" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="635" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q634">
+        <v>2</v>
+      </c>
+      <c r="S634" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="635" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>883</v>
       </c>
@@ -34812,8 +36354,14 @@
       <c r="P635" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="636" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q635">
+        <v>0</v>
+      </c>
+      <c r="S635" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="636" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>883</v>
       </c>
@@ -34856,8 +36404,14 @@
       <c r="P636" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="637" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q636">
+        <v>2</v>
+      </c>
+      <c r="S636" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="637" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>883</v>
       </c>
@@ -34900,8 +36454,14 @@
       <c r="P637" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="638" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q637">
+        <v>2</v>
+      </c>
+      <c r="S637" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="638" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>883</v>
       </c>
@@ -34944,8 +36504,14 @@
       <c r="P638" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="639" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q638">
+        <v>2</v>
+      </c>
+      <c r="S638" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="639" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>883</v>
       </c>
@@ -34988,8 +36554,14 @@
       <c r="P639" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="640" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q639">
+        <v>1</v>
+      </c>
+      <c r="S639" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="640" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>883</v>
       </c>
@@ -35032,8 +36604,14 @@
       <c r="P640" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="641" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q640">
+        <v>1</v>
+      </c>
+      <c r="S640" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="641" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>883</v>
       </c>
@@ -35076,8 +36654,14 @@
       <c r="P641" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="642" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q641">
+        <v>1</v>
+      </c>
+      <c r="S641" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="642" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>883</v>
       </c>
@@ -35120,8 +36704,14 @@
       <c r="P642" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="643" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q642">
+        <v>0</v>
+      </c>
+      <c r="S642" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="643" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>883</v>
       </c>
@@ -35164,8 +36754,14 @@
       <c r="P643" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="644" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q643">
+        <v>2</v>
+      </c>
+      <c r="S643" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="644" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>883</v>
       </c>
@@ -35208,8 +36804,14 @@
       <c r="P644" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="645" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q644">
+        <v>1</v>
+      </c>
+      <c r="S644" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="645" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>883</v>
       </c>
@@ -35252,8 +36854,14 @@
       <c r="P645" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="646" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q645">
+        <v>0</v>
+      </c>
+      <c r="S645" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="646" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>883</v>
       </c>
@@ -35296,8 +36904,14 @@
       <c r="P646" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="647" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q646">
+        <v>1</v>
+      </c>
+      <c r="S646" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="647" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>883</v>
       </c>
@@ -35346,8 +36960,14 @@
       <c r="P647" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="648" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q647">
+        <v>2</v>
+      </c>
+      <c r="S647" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="648" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>883</v>
       </c>
@@ -35390,8 +37010,14 @@
       <c r="P648" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="649" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q648">
+        <v>2</v>
+      </c>
+      <c r="S648" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="649" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>883</v>
       </c>
@@ -35434,8 +37060,14 @@
       <c r="P649" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="650" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q649">
+        <v>2</v>
+      </c>
+      <c r="S649" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="650" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>883</v>
       </c>
@@ -35478,8 +37110,14 @@
       <c r="P650" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="651" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q650">
+        <v>0</v>
+      </c>
+      <c r="S650" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="651" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>889</v>
       </c>
@@ -35522,8 +37160,14 @@
       <c r="P651" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="652" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q651">
+        <v>1</v>
+      </c>
+      <c r="S651" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="652" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>889</v>
       </c>
@@ -35566,8 +37210,14 @@
       <c r="P652" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="653" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q652">
+        <v>1</v>
+      </c>
+      <c r="S652" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="653" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>889</v>
       </c>
@@ -35610,8 +37260,14 @@
       <c r="P653" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="654" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q653">
+        <v>1</v>
+      </c>
+      <c r="S653" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="654" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>889</v>
       </c>
@@ -35654,8 +37310,14 @@
       <c r="P654" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="655" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q654">
+        <v>2</v>
+      </c>
+      <c r="S654" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="655" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>889</v>
       </c>
@@ -35698,8 +37360,14 @@
       <c r="P655" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="656" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q655">
+        <v>1</v>
+      </c>
+      <c r="S655" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="656" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>889</v>
       </c>
@@ -35742,8 +37410,14 @@
       <c r="P656" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="657" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q656">
+        <v>2</v>
+      </c>
+      <c r="S656" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="657" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>889</v>
       </c>
@@ -35786,8 +37460,14 @@
       <c r="P657" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="658" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q657">
+        <v>2</v>
+      </c>
+      <c r="S657" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="658" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>889</v>
       </c>
@@ -35830,8 +37510,14 @@
       <c r="P658" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="659" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q658">
+        <v>1</v>
+      </c>
+      <c r="S658" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="659" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>889</v>
       </c>
@@ -35874,8 +37560,14 @@
       <c r="P659" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="660" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q659">
+        <v>1</v>
+      </c>
+      <c r="S659" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="660" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>889</v>
       </c>
@@ -35918,8 +37610,14 @@
       <c r="P660" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="661" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q660">
+        <v>1</v>
+      </c>
+      <c r="S660" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="661" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>889</v>
       </c>
@@ -35962,8 +37660,14 @@
       <c r="P661" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="662" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q661">
+        <v>1</v>
+      </c>
+      <c r="S661" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="662" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>889</v>
       </c>
@@ -36006,8 +37710,14 @@
       <c r="P662" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="663" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q662">
+        <v>1</v>
+      </c>
+      <c r="S662" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="663" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>889</v>
       </c>
@@ -36050,8 +37760,14 @@
       <c r="P663" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="664" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q663">
+        <v>1</v>
+      </c>
+      <c r="S663" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="664" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>889</v>
       </c>
@@ -36094,8 +37810,14 @@
       <c r="P664" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="665" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q664">
+        <v>1</v>
+      </c>
+      <c r="S664" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="665" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>889</v>
       </c>
@@ -36138,8 +37860,14 @@
       <c r="P665" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="666" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q665">
+        <v>1</v>
+      </c>
+      <c r="S665" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="666" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A666" t="s">
         <v>889</v>
       </c>
@@ -36182,8 +37910,14 @@
       <c r="P666" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="667" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q666">
+        <v>1</v>
+      </c>
+      <c r="S666" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="667" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A667" t="s">
         <v>889</v>
       </c>
@@ -36226,8 +37960,14 @@
       <c r="P667" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="668" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q667">
+        <v>1</v>
+      </c>
+      <c r="S667" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="668" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>889</v>
       </c>
@@ -36270,8 +38010,14 @@
       <c r="P668" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="669" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q668">
+        <v>1</v>
+      </c>
+      <c r="S668" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="669" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>889</v>
       </c>
@@ -36314,8 +38060,14 @@
       <c r="P669" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="670" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q669">
+        <v>2</v>
+      </c>
+      <c r="S669" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="670" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>889</v>
       </c>
@@ -36358,8 +38110,14 @@
       <c r="P670" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="671" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q670">
+        <v>1</v>
+      </c>
+      <c r="S670" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="671" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>906</v>
       </c>
@@ -36402,8 +38160,14 @@
       <c r="P671" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="672" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q671">
+        <v>2</v>
+      </c>
+      <c r="S671" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="672" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>906</v>
       </c>
@@ -36446,8 +38210,14 @@
       <c r="P672" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="673" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q672">
+        <v>2</v>
+      </c>
+      <c r="S672" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="673" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>906</v>
       </c>
@@ -36490,8 +38260,14 @@
       <c r="P673" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="674" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q673">
+        <v>0</v>
+      </c>
+      <c r="S673" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="674" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>906</v>
       </c>
@@ -36534,8 +38310,14 @@
       <c r="P674" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="675" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q674">
+        <v>0</v>
+      </c>
+      <c r="S674" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="675" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>906</v>
       </c>
@@ -36578,8 +38360,14 @@
       <c r="P675" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="676" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q675">
+        <v>2</v>
+      </c>
+      <c r="S675" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="676" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>906</v>
       </c>
@@ -36622,8 +38410,14 @@
       <c r="P676" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="677" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q676">
+        <v>0</v>
+      </c>
+      <c r="S676" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="677" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>906</v>
       </c>
@@ -36666,8 +38460,14 @@
       <c r="P677" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="678" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q677">
+        <v>0</v>
+      </c>
+      <c r="S677" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="678" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>906</v>
       </c>
@@ -36710,8 +38510,14 @@
       <c r="P678" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="679" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q678">
+        <v>1</v>
+      </c>
+      <c r="S678" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="679" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>906</v>
       </c>
@@ -36754,8 +38560,14 @@
       <c r="P679" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="680" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q679">
+        <v>0</v>
+      </c>
+      <c r="S679" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="680" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>906</v>
       </c>
@@ -36798,8 +38610,14 @@
       <c r="P680" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="681" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q680">
+        <v>2</v>
+      </c>
+      <c r="S680" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="681" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>906</v>
       </c>
@@ -36842,8 +38660,14 @@
       <c r="P681" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="682" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q681">
+        <v>0</v>
+      </c>
+      <c r="S681" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="682" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>906</v>
       </c>
@@ -36886,8 +38710,14 @@
       <c r="P682" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="683" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q682">
+        <v>1</v>
+      </c>
+      <c r="S682" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="683" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>906</v>
       </c>
@@ -36930,8 +38760,14 @@
       <c r="P683" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="684" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q683">
+        <v>0</v>
+      </c>
+      <c r="S683" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="684" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>906</v>
       </c>
@@ -36974,8 +38810,14 @@
       <c r="P684" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="685" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q684">
+        <v>0</v>
+      </c>
+      <c r="S684" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="685" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>906</v>
       </c>
@@ -37018,8 +38860,14 @@
       <c r="P685" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="686" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q685">
+        <v>1</v>
+      </c>
+      <c r="S685" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="686" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>906</v>
       </c>
@@ -37062,8 +38910,14 @@
       <c r="P686" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="687" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q686">
+        <v>2</v>
+      </c>
+      <c r="S686" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="687" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>906</v>
       </c>
@@ -37106,8 +38960,14 @@
       <c r="P687" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="688" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q687">
+        <v>2</v>
+      </c>
+      <c r="S687" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="688" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>906</v>
       </c>
@@ -37150,8 +39010,14 @@
       <c r="P688" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="689" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q688">
+        <v>2</v>
+      </c>
+      <c r="S688" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="689" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>906</v>
       </c>
@@ -37194,8 +39060,14 @@
       <c r="P689" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="690" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q689">
+        <v>2</v>
+      </c>
+      <c r="S689" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="690" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>906</v>
       </c>
@@ -37238,8 +39110,14 @@
       <c r="P690" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="691" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q690">
+        <v>0</v>
+      </c>
+      <c r="S690" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="691" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>919</v>
       </c>
@@ -37282,8 +39160,14 @@
       <c r="P691" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="692" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q691">
+        <v>1</v>
+      </c>
+      <c r="S691" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="692" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>919</v>
       </c>
@@ -37326,8 +39210,14 @@
       <c r="P692" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="693" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q692">
+        <v>1</v>
+      </c>
+      <c r="S692" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="693" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>919</v>
       </c>
@@ -37376,8 +39266,14 @@
       <c r="P693" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="694" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q693">
+        <v>1</v>
+      </c>
+      <c r="S693" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="694" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A694" t="s">
         <v>919</v>
       </c>
@@ -37420,8 +39316,14 @@
       <c r="P694" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="695" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q694">
+        <v>1</v>
+      </c>
+      <c r="S694" t="s">
+        <v>1332</v>
+      </c>
+    </row>
+    <row r="695" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>919</v>
       </c>
@@ -37464,8 +39366,14 @@
       <c r="P695" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="696" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q695">
+        <v>0</v>
+      </c>
+      <c r="S695" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="696" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>919</v>
       </c>
@@ -37508,8 +39416,14 @@
       <c r="P696" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="697" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q696">
+        <v>0</v>
+      </c>
+      <c r="S696" s="1" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="697" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>919</v>
       </c>
@@ -37552,8 +39466,14 @@
       <c r="P697" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="698" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q697">
+        <v>1</v>
+      </c>
+      <c r="S697" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="698" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>919</v>
       </c>
@@ -37596,8 +39516,14 @@
       <c r="P698" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="699" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q698">
+        <v>0</v>
+      </c>
+      <c r="S698" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="699" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>919</v>
       </c>
@@ -37640,8 +39566,14 @@
       <c r="P699" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="700" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q699">
+        <v>1</v>
+      </c>
+      <c r="S699" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="700" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>919</v>
       </c>
@@ -37684,8 +39616,14 @@
       <c r="P700" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="701" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q700">
+        <v>1</v>
+      </c>
+      <c r="S700" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="701" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>919</v>
       </c>
@@ -37728,8 +39666,14 @@
       <c r="P701" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="702" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q701">
+        <v>1</v>
+      </c>
+      <c r="S701" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="702" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>919</v>
       </c>
@@ -37772,8 +39716,14 @@
       <c r="P702" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="703" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q702">
+        <v>0</v>
+      </c>
+      <c r="S702" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="703" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>919</v>
       </c>
@@ -37816,8 +39766,14 @@
       <c r="P703" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="704" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q703">
+        <v>2</v>
+      </c>
+      <c r="S703" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="704" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>919</v>
       </c>
@@ -37860,8 +39816,14 @@
       <c r="P704" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="705" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q704">
+        <v>1</v>
+      </c>
+      <c r="S704" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="705" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>919</v>
       </c>
@@ -37904,8 +39866,14 @@
       <c r="P705" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="706" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q705">
+        <v>0</v>
+      </c>
+      <c r="S705" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="706" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>919</v>
       </c>
@@ -37948,8 +39916,14 @@
       <c r="P706" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="707" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q706">
+        <v>1</v>
+      </c>
+      <c r="S706" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="707" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>919</v>
       </c>
@@ -37992,8 +39966,14 @@
       <c r="P707" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="708" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q707">
+        <v>1</v>
+      </c>
+      <c r="S707" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="708" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>919</v>
       </c>
@@ -38036,8 +40016,14 @@
       <c r="P708" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="709" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q708">
+        <v>0</v>
+      </c>
+      <c r="S708" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="709" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>919</v>
       </c>
@@ -38080,8 +40066,14 @@
       <c r="P709" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="710" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q709">
+        <v>1</v>
+      </c>
+      <c r="S709" s="1" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="710" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>933</v>
       </c>
@@ -38124,8 +40116,14 @@
       <c r="P710" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="711" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q710">
+        <v>1</v>
+      </c>
+      <c r="S710" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="711" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>933</v>
       </c>
@@ -38174,8 +40172,14 @@
       <c r="P711" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="712" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q711">
+        <v>2</v>
+      </c>
+      <c r="S711" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="712" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>933</v>
       </c>
@@ -38218,8 +40222,14 @@
       <c r="P712" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="713" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q712">
+        <v>1</v>
+      </c>
+      <c r="S712" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="713" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>933</v>
       </c>
@@ -38262,8 +40272,14 @@
       <c r="P713" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="714" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q713">
+        <v>1</v>
+      </c>
+      <c r="S713" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="714" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>933</v>
       </c>
@@ -38306,8 +40322,14 @@
       <c r="P714" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="715" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q714">
+        <v>1</v>
+      </c>
+      <c r="S714" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="715" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>933</v>
       </c>
@@ -38350,8 +40372,14 @@
       <c r="P715" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="716" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q715">
+        <v>0</v>
+      </c>
+      <c r="S715" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="716" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>933</v>
       </c>
@@ -38394,8 +40422,14 @@
       <c r="P716" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="717" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q716">
+        <v>0</v>
+      </c>
+      <c r="S716" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="717" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>933</v>
       </c>
@@ -38438,8 +40472,14 @@
       <c r="P717" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="718" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q717">
+        <v>2</v>
+      </c>
+      <c r="S717" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="718" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A718" t="s">
         <v>933</v>
       </c>
@@ -38482,8 +40522,14 @@
       <c r="P718" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="719" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q718">
+        <v>1</v>
+      </c>
+      <c r="S718" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="719" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>933</v>
       </c>
@@ -38526,8 +40572,14 @@
       <c r="P719" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="720" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q719">
+        <v>1</v>
+      </c>
+      <c r="S719" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="720" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>933</v>
       </c>
@@ -38570,8 +40622,14 @@
       <c r="P720" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="721" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q720">
+        <v>1</v>
+      </c>
+      <c r="S720" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="721" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A721" t="s">
         <v>933</v>
       </c>
@@ -38614,8 +40672,14 @@
       <c r="P721" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="722" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q721">
+        <v>1</v>
+      </c>
+      <c r="S721" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="722" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>933</v>
       </c>
@@ -38658,8 +40722,14 @@
       <c r="P722" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="723" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q722">
+        <v>1</v>
+      </c>
+      <c r="S722" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="723" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>933</v>
       </c>
@@ -38702,8 +40772,14 @@
       <c r="P723" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="724" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q723">
+        <v>1</v>
+      </c>
+      <c r="S723" t="s">
+        <v>1340</v>
+      </c>
+    </row>
+    <row r="724" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A724" t="s">
         <v>933</v>
       </c>
@@ -38746,8 +40822,14 @@
       <c r="P724" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="725" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q724">
+        <v>1</v>
+      </c>
+      <c r="S724" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="725" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>933</v>
       </c>
@@ -38790,8 +40872,14 @@
       <c r="P725" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="726" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q725">
+        <v>1</v>
+      </c>
+      <c r="S725" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="726" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>933</v>
       </c>
@@ -38834,8 +40922,14 @@
       <c r="P726" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="727" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q726">
+        <v>0</v>
+      </c>
+      <c r="S726" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="727" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A727" t="s">
         <v>933</v>
       </c>
@@ -38875,8 +40969,14 @@
       <c r="P727" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="728" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q727">
+        <v>1</v>
+      </c>
+      <c r="S727" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="728" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>933</v>
       </c>
@@ -38919,8 +41019,14 @@
       <c r="P728" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="729" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q728">
+        <v>1</v>
+      </c>
+      <c r="S728" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="729" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>942</v>
       </c>
@@ -38969,8 +41075,14 @@
       <c r="P729" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="730" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q729">
+        <v>1</v>
+      </c>
+      <c r="S729" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="730" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>942</v>
       </c>
@@ -39013,8 +41125,14 @@
       <c r="P730" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="731" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q730">
+        <v>1</v>
+      </c>
+      <c r="S730" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="731" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>942</v>
       </c>
@@ -39057,8 +41175,14 @@
       <c r="P731" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="732" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q731">
+        <v>1</v>
+      </c>
+      <c r="S731" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="732" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>942</v>
       </c>
@@ -39101,8 +41225,14 @@
       <c r="P732" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="733" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q732">
+        <v>1</v>
+      </c>
+      <c r="S732" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="733" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>942</v>
       </c>
@@ -39145,8 +41275,14 @@
       <c r="P733" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="734" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q733">
+        <v>0</v>
+      </c>
+      <c r="S733" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="734" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>942</v>
       </c>
@@ -39189,8 +41325,14 @@
       <c r="P734" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="735" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q734">
+        <v>1</v>
+      </c>
+      <c r="S734" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="735" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>942</v>
       </c>
@@ -39233,8 +41375,14 @@
       <c r="P735" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="736" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q735">
+        <v>1</v>
+      </c>
+      <c r="S735" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="736" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>942</v>
       </c>
@@ -39277,8 +41425,14 @@
       <c r="P736" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="737" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q736">
+        <v>1</v>
+      </c>
+      <c r="S736" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="737" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>942</v>
       </c>
@@ -39321,8 +41475,14 @@
       <c r="P737" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="738" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q737">
+        <v>0</v>
+      </c>
+      <c r="S737" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="738" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>942</v>
       </c>
@@ -39365,8 +41525,14 @@
       <c r="P738" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="739" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q738">
+        <v>1</v>
+      </c>
+      <c r="S738" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="739" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>942</v>
       </c>
@@ -39409,8 +41575,14 @@
       <c r="P739" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="740" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q739">
+        <v>2</v>
+      </c>
+      <c r="S739" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="740" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>942</v>
       </c>
@@ -39459,8 +41631,14 @@
       <c r="P740" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="741" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q740">
+        <v>1</v>
+      </c>
+      <c r="S740" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="741" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>942</v>
       </c>
@@ -39503,8 +41681,14 @@
       <c r="P741" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="742" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q741">
+        <v>2</v>
+      </c>
+      <c r="S741" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="742" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>942</v>
       </c>
@@ -39547,8 +41731,14 @@
       <c r="P742" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="743" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q742">
+        <v>1</v>
+      </c>
+      <c r="S742" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="743" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>942</v>
       </c>
@@ -39591,8 +41781,14 @@
       <c r="P743" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="744" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q743">
+        <v>2</v>
+      </c>
+      <c r="S743" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="744" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>942</v>
       </c>
@@ -39635,8 +41831,14 @@
       <c r="P744" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="745" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q744">
+        <v>0</v>
+      </c>
+      <c r="S744" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="745" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>942</v>
       </c>
@@ -39679,8 +41881,14 @@
       <c r="P745" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="746" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q745">
+        <v>2</v>
+      </c>
+      <c r="S745" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="746" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>942</v>
       </c>
@@ -39723,8 +41931,14 @@
       <c r="P746" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="747" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q746">
+        <v>2</v>
+      </c>
+      <c r="S746" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="747" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>949</v>
       </c>
@@ -39767,8 +41981,14 @@
       <c r="P747" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="748" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q747">
+        <v>2</v>
+      </c>
+      <c r="S747" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="748" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>949</v>
       </c>
@@ -39811,8 +42031,14 @@
       <c r="P748" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="749" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q748">
+        <v>1</v>
+      </c>
+      <c r="S748" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="749" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>949</v>
       </c>
@@ -39855,8 +42081,14 @@
       <c r="P749" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="750" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q749">
+        <v>1</v>
+      </c>
+      <c r="S749" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="750" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>949</v>
       </c>
@@ -39899,8 +42131,14 @@
       <c r="P750" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="751" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q750">
+        <v>1</v>
+      </c>
+      <c r="S750" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="751" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>949</v>
       </c>
@@ -39943,8 +42181,14 @@
       <c r="P751" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="752" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q751">
+        <v>2</v>
+      </c>
+      <c r="S751" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="752" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>949</v>
       </c>
@@ -39987,8 +42231,14 @@
       <c r="P752" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="753" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q752">
+        <v>2</v>
+      </c>
+      <c r="S752" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="753" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>949</v>
       </c>
@@ -40031,8 +42281,14 @@
       <c r="P753" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="754" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q753">
+        <v>2</v>
+      </c>
+      <c r="S753" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="754" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>949</v>
       </c>
@@ -40075,8 +42331,14 @@
       <c r="P754" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="755" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q754">
+        <v>2</v>
+      </c>
+      <c r="S754" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="755" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>949</v>
       </c>
@@ -40119,8 +42381,14 @@
       <c r="P755" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="756" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q755">
+        <v>2</v>
+      </c>
+      <c r="S755" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="756" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>949</v>
       </c>
@@ -40163,8 +42431,14 @@
       <c r="P756" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="757" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q756">
+        <v>2</v>
+      </c>
+      <c r="S756" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="757" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>949</v>
       </c>
@@ -40207,8 +42481,14 @@
       <c r="P757" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="758" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q757">
+        <v>0</v>
+      </c>
+      <c r="S757" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="758" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>949</v>
       </c>
@@ -40251,8 +42531,14 @@
       <c r="P758" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="759" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q758">
+        <v>1</v>
+      </c>
+      <c r="S758" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="759" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>949</v>
       </c>
@@ -40295,8 +42581,14 @@
       <c r="P759" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="760" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q759">
+        <v>2</v>
+      </c>
+      <c r="S759" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="760" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>949</v>
       </c>
@@ -40339,8 +42631,14 @@
       <c r="P760" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="761" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q760">
+        <v>1</v>
+      </c>
+      <c r="S760" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="761" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>949</v>
       </c>
@@ -40383,8 +42681,14 @@
       <c r="P761" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="762" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q761">
+        <v>0</v>
+      </c>
+      <c r="S761" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="762" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>949</v>
       </c>
@@ -40427,8 +42731,14 @@
       <c r="P762" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="763" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q762">
+        <v>0</v>
+      </c>
+      <c r="S762" s="1" t="s">
+        <v>1334</v>
+      </c>
+    </row>
+    <row r="763" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>949</v>
       </c>
@@ -40471,8 +42781,14 @@
       <c r="P763" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="764" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q763">
+        <v>1</v>
+      </c>
+      <c r="S763" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="764" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>949</v>
       </c>
@@ -40515,8 +42831,14 @@
       <c r="P764" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="765" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q764">
+        <v>1</v>
+      </c>
+      <c r="S764" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="765" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>949</v>
       </c>
@@ -40559,8 +42881,14 @@
       <c r="P765" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="766" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q765">
+        <v>1</v>
+      </c>
+      <c r="S765" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="766" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>949</v>
       </c>
@@ -40603,8 +42931,14 @@
       <c r="P766" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="767" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q766">
+        <v>2</v>
+      </c>
+      <c r="S766" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="767" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>951</v>
       </c>
@@ -40647,8 +42981,14 @@
       <c r="P767" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="768" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q767">
+        <v>2</v>
+      </c>
+      <c r="S767" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="768" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>951</v>
       </c>
@@ -40697,8 +43037,14 @@
       <c r="P768" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="769" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q768">
+        <v>2</v>
+      </c>
+      <c r="S768" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="769" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>951</v>
       </c>
@@ -40741,8 +43087,14 @@
       <c r="P769" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="770" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q769">
+        <v>2</v>
+      </c>
+      <c r="S769" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="770" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>951</v>
       </c>
@@ -40791,8 +43143,14 @@
       <c r="P770" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="771" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q770">
+        <v>2</v>
+      </c>
+      <c r="S770" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="771" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>951</v>
       </c>
@@ -40835,8 +43193,14 @@
       <c r="P771" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="772" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q771">
+        <v>1</v>
+      </c>
+      <c r="S771" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="772" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>951</v>
       </c>
@@ -40879,8 +43243,14 @@
       <c r="P772" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="773" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q772">
+        <v>2</v>
+      </c>
+      <c r="S772" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="773" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>951</v>
       </c>
@@ -40923,8 +43293,14 @@
       <c r="P773" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="774" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q773">
+        <v>2</v>
+      </c>
+      <c r="S773" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="774" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A774" t="s">
         <v>951</v>
       </c>
@@ -40967,8 +43343,14 @@
       <c r="P774" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="775" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q774">
+        <v>2</v>
+      </c>
+      <c r="S774" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="775" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>951</v>
       </c>
@@ -41011,8 +43393,14 @@
       <c r="P775" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="776" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q775">
+        <v>2</v>
+      </c>
+      <c r="S775" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="776" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>951</v>
       </c>
@@ -41055,8 +43443,14 @@
       <c r="P776" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="777" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q776">
+        <v>2</v>
+      </c>
+      <c r="S776" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="777" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>951</v>
       </c>
@@ -41099,8 +43493,14 @@
       <c r="P777" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="778" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q777">
+        <v>2</v>
+      </c>
+      <c r="S777" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="778" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>951</v>
       </c>
@@ -41143,8 +43543,14 @@
       <c r="P778" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="779" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q778">
+        <v>2</v>
+      </c>
+      <c r="S778" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="779" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>951</v>
       </c>
@@ -41187,8 +43593,14 @@
       <c r="P779" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="780" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q779">
+        <v>1</v>
+      </c>
+      <c r="S779" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="780" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>951</v>
       </c>
@@ -41231,8 +43643,14 @@
       <c r="P780" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="781" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q780">
+        <v>1</v>
+      </c>
+      <c r="S780" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="781" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A781" t="s">
         <v>951</v>
       </c>
@@ -41275,8 +43693,14 @@
       <c r="P781" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="782" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q781">
+        <v>0</v>
+      </c>
+      <c r="S781" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="782" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>951</v>
       </c>
@@ -41319,8 +43743,14 @@
       <c r="P782" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="783" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q782">
+        <v>2</v>
+      </c>
+      <c r="S782" s="1" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="783" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>951</v>
       </c>
@@ -41363,8 +43793,14 @@
       <c r="P783" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="784" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q783">
+        <v>1</v>
+      </c>
+      <c r="S783" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="784" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>951</v>
       </c>
@@ -41407,8 +43843,14 @@
       <c r="P784" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="785" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q784">
+        <v>1</v>
+      </c>
+      <c r="S784" s="1" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="785" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>959</v>
       </c>
@@ -41451,8 +43893,15 @@
       <c r="P785" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="786" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q785">
+        <v>1</v>
+      </c>
+      <c r="S785" t="str">
+        <f>IF(Q785=2,"ok",IF(Q785=1,"Phù hợp 1 phần", "ko hợp"))</f>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="786" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>959</v>
       </c>
@@ -41495,8 +43944,15 @@
       <c r="P786" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="787" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q786">
+        <v>2</v>
+      </c>
+      <c r="S786" t="str">
+        <f t="shared" ref="S786:S907" si="0">IF(Q786=2,"ok",IF(Q786=1,"Phù hợp 1 phần", "ko hợp"))</f>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="787" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>959</v>
       </c>
@@ -41539,8 +43995,15 @@
       <c r="P787" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="788" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q787">
+        <v>1</v>
+      </c>
+      <c r="S787" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="788" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>959</v>
       </c>
@@ -41583,8 +44046,15 @@
       <c r="P788" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="789" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q788">
+        <v>1</v>
+      </c>
+      <c r="S788" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="789" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A789" t="s">
         <v>959</v>
       </c>
@@ -41627,8 +44097,15 @@
       <c r="P789" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="790" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q789">
+        <v>1</v>
+      </c>
+      <c r="S789" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="790" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>959</v>
       </c>
@@ -41671,8 +44148,15 @@
       <c r="P790" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="791" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q790">
+        <v>2</v>
+      </c>
+      <c r="S790" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="791" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>959</v>
       </c>
@@ -41715,8 +44199,15 @@
       <c r="P791" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="792" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q791">
+        <v>1</v>
+      </c>
+      <c r="S791" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="792" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A792" t="s">
         <v>959</v>
       </c>
@@ -41759,8 +44250,15 @@
       <c r="P792" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="793" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q792">
+        <v>2</v>
+      </c>
+      <c r="S792" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="793" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>959</v>
       </c>
@@ -41809,8 +44307,15 @@
       <c r="P793" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="794" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q793">
+        <v>2</v>
+      </c>
+      <c r="S793" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="794" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>959</v>
       </c>
@@ -41853,8 +44358,15 @@
       <c r="P794" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="795" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q794">
+        <v>1</v>
+      </c>
+      <c r="S794" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="795" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>959</v>
       </c>
@@ -41897,8 +44409,15 @@
       <c r="P795" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="796" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q795">
+        <v>2</v>
+      </c>
+      <c r="S795" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="796" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>959</v>
       </c>
@@ -41941,8 +44460,15 @@
       <c r="P796" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="797" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q796">
+        <v>1</v>
+      </c>
+      <c r="S796" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="797" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>959</v>
       </c>
@@ -41985,8 +44511,15 @@
       <c r="P797" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="798" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q797">
+        <v>0</v>
+      </c>
+      <c r="S797" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="798" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>959</v>
       </c>
@@ -42029,8 +44562,15 @@
       <c r="P798" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="799" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q798">
+        <v>1</v>
+      </c>
+      <c r="S798" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="799" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>959</v>
       </c>
@@ -42073,8 +44613,15 @@
       <c r="P799" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="800" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q799">
+        <v>2</v>
+      </c>
+      <c r="S799" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="800" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>959</v>
       </c>
@@ -42117,8 +44664,15 @@
       <c r="P800" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="801" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q800">
+        <v>2</v>
+      </c>
+      <c r="S800" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="801" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>959</v>
       </c>
@@ -42161,8 +44715,15 @@
       <c r="P801" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="802" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q801">
+        <v>2</v>
+      </c>
+      <c r="S801" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="802" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>959</v>
       </c>
@@ -42205,8 +44766,15 @@
       <c r="P802" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="803" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q802">
+        <v>1</v>
+      </c>
+      <c r="S802" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="803" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>959</v>
       </c>
@@ -42249,8 +44817,15 @@
       <c r="P803" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="804" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q803">
+        <v>1</v>
+      </c>
+      <c r="S803" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="804" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>965</v>
       </c>
@@ -42293,8 +44868,15 @@
       <c r="P804" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="805" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q804">
+        <v>2</v>
+      </c>
+      <c r="S804" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="805" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>965</v>
       </c>
@@ -42337,8 +44919,15 @@
       <c r="P805" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="806" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q805">
+        <v>1</v>
+      </c>
+      <c r="S805" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="806" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A806" t="s">
         <v>965</v>
       </c>
@@ -42381,8 +44970,15 @@
       <c r="P806" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="807" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q806">
+        <v>1</v>
+      </c>
+      <c r="S806" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="807" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>965</v>
       </c>
@@ -42425,8 +45021,15 @@
       <c r="P807" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="808" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q807">
+        <v>1</v>
+      </c>
+      <c r="S807" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="808" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A808" t="s">
         <v>965</v>
       </c>
@@ -42469,8 +45072,15 @@
       <c r="P808" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="809" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q808">
+        <v>2</v>
+      </c>
+      <c r="S808" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="809" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>965</v>
       </c>
@@ -42513,8 +45123,15 @@
       <c r="P809" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="810" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q809">
+        <v>2</v>
+      </c>
+      <c r="S809" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="810" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>965</v>
       </c>
@@ -42557,8 +45174,15 @@
       <c r="P810" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="811" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q810">
+        <v>2</v>
+      </c>
+      <c r="S810" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="811" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>965</v>
       </c>
@@ -42601,8 +45225,15 @@
       <c r="P811" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="812" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q811">
+        <v>0</v>
+      </c>
+      <c r="S811" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="812" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>965</v>
       </c>
@@ -42645,8 +45276,15 @@
       <c r="P812" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="813" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q812">
+        <v>2</v>
+      </c>
+      <c r="S812" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="813" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>965</v>
       </c>
@@ -42689,8 +45327,15 @@
       <c r="P813" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="814" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q813">
+        <v>1</v>
+      </c>
+      <c r="S813" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="814" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A814" t="s">
         <v>965</v>
       </c>
@@ -42733,8 +45378,15 @@
       <c r="P814" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="815" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q814">
+        <v>1</v>
+      </c>
+      <c r="S814" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="815" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>965</v>
       </c>
@@ -42777,8 +45429,15 @@
       <c r="P815" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="816" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q815">
+        <v>1</v>
+      </c>
+      <c r="S815" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="816" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A816" t="s">
         <v>965</v>
       </c>
@@ -42821,8 +45480,15 @@
       <c r="P816" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="817" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q816">
+        <v>0</v>
+      </c>
+      <c r="S816" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="817" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>965</v>
       </c>
@@ -42865,8 +45531,15 @@
       <c r="P817" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="818" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q817">
+        <v>1</v>
+      </c>
+      <c r="S817" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="818" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A818" t="s">
         <v>965</v>
       </c>
@@ -42909,8 +45582,15 @@
       <c r="P818" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="819" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q818">
+        <v>1</v>
+      </c>
+      <c r="S818" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="819" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>965</v>
       </c>
@@ -42953,8 +45633,15 @@
       <c r="P819" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="820" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q819">
+        <v>0</v>
+      </c>
+      <c r="S819" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="820" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>965</v>
       </c>
@@ -42997,8 +45684,15 @@
       <c r="P820" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="821" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q820">
+        <v>1</v>
+      </c>
+      <c r="S820" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="821" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>965</v>
       </c>
@@ -43041,8 +45735,15 @@
       <c r="P821" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="822" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q821">
+        <v>1</v>
+      </c>
+      <c r="S821" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="822" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>965</v>
       </c>
@@ -43085,8 +45786,15 @@
       <c r="P822" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="823" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q822">
+        <v>1</v>
+      </c>
+      <c r="S822" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="823" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>965</v>
       </c>
@@ -43129,8 +45837,15 @@
       <c r="P823" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="824" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q823">
+        <v>1</v>
+      </c>
+      <c r="S823" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="824" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A824" t="s">
         <v>971</v>
       </c>
@@ -43173,8 +45888,15 @@
       <c r="P824" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="825" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q824">
+        <v>1</v>
+      </c>
+      <c r="S824" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="825" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>971</v>
       </c>
@@ -43217,8 +45939,15 @@
       <c r="P825" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="826" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q825">
+        <v>2</v>
+      </c>
+      <c r="S825" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="826" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>971</v>
       </c>
@@ -43267,8 +45996,15 @@
       <c r="P826" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="827" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q826">
+        <v>2</v>
+      </c>
+      <c r="S826" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="827" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>971</v>
       </c>
@@ -43311,8 +46047,15 @@
       <c r="P827" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="828" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q827">
+        <v>1</v>
+      </c>
+      <c r="S827" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="828" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>971</v>
       </c>
@@ -43355,8 +46098,15 @@
       <c r="P828" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="829" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q828">
+        <v>2</v>
+      </c>
+      <c r="S828" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="829" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>971</v>
       </c>
@@ -43405,8 +46155,15 @@
       <c r="P829" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="830" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q829">
+        <v>2</v>
+      </c>
+      <c r="S829" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="830" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>971</v>
       </c>
@@ -43449,8 +46206,15 @@
       <c r="P830" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="831" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q830">
+        <v>1</v>
+      </c>
+      <c r="S830" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="831" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>971</v>
       </c>
@@ -43493,8 +46257,15 @@
       <c r="P831" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="832" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q831">
+        <v>2</v>
+      </c>
+      <c r="S831" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="832" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>971</v>
       </c>
@@ -43537,8 +46308,15 @@
       <c r="P832" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="833" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q832">
+        <v>2</v>
+      </c>
+      <c r="S832" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="833" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>971</v>
       </c>
@@ -43581,8 +46359,15 @@
       <c r="P833" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="834" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q833">
+        <v>1</v>
+      </c>
+      <c r="S833" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="834" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A834" t="s">
         <v>971</v>
       </c>
@@ -43631,8 +46416,15 @@
       <c r="P834" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="835" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q834">
+        <v>2</v>
+      </c>
+      <c r="S834" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="835" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A835" t="s">
         <v>971</v>
       </c>
@@ -43681,8 +46473,15 @@
       <c r="P835" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="836" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q835">
+        <v>2</v>
+      </c>
+      <c r="S835" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="836" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A836" t="s">
         <v>971</v>
       </c>
@@ -43725,8 +46524,15 @@
       <c r="P836" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="837" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q836">
+        <v>0</v>
+      </c>
+      <c r="S836" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="837" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A837" t="s">
         <v>971</v>
       </c>
@@ -43769,8 +46575,15 @@
       <c r="P837" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="838" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q837">
+        <v>1</v>
+      </c>
+      <c r="S837" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="838" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A838" t="s">
         <v>971</v>
       </c>
@@ -43813,8 +46626,15 @@
       <c r="P838" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="839" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q838">
+        <v>1</v>
+      </c>
+      <c r="S838" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="839" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A839" t="s">
         <v>971</v>
       </c>
@@ -43857,8 +46677,15 @@
       <c r="P839" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="840" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q839">
+        <v>0</v>
+      </c>
+      <c r="S839" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="840" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A840" t="s">
         <v>973</v>
       </c>
@@ -43907,8 +46734,15 @@
       <c r="P840" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="841" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q840">
+        <v>2</v>
+      </c>
+      <c r="S840" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="841" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A841" t="s">
         <v>973</v>
       </c>
@@ -43951,8 +46785,15 @@
       <c r="P841" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="842" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q841">
+        <v>1</v>
+      </c>
+      <c r="S841" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="842" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A842" t="s">
         <v>973</v>
       </c>
@@ -44001,8 +46842,15 @@
       <c r="P842" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="843" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q842">
+        <v>2</v>
+      </c>
+      <c r="S842" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="843" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A843" t="s">
         <v>973</v>
       </c>
@@ -44051,8 +46899,15 @@
       <c r="P843" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="844" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q843">
+        <v>2</v>
+      </c>
+      <c r="S843" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="844" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A844" t="s">
         <v>973</v>
       </c>
@@ -44101,8 +46956,15 @@
       <c r="P844" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="845" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q844">
+        <v>2</v>
+      </c>
+      <c r="S844" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="845" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A845" t="s">
         <v>973</v>
       </c>
@@ -44145,8 +47007,15 @@
       <c r="P845" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="846" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q845">
+        <v>1</v>
+      </c>
+      <c r="S845" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="846" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A846" t="s">
         <v>973</v>
       </c>
@@ -44189,8 +47058,15 @@
       <c r="P846" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="847" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q846">
+        <v>1</v>
+      </c>
+      <c r="S846" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="847" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A847" t="s">
         <v>973</v>
       </c>
@@ -44233,8 +47109,15 @@
       <c r="P847" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="848" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q847">
+        <v>2</v>
+      </c>
+      <c r="S847" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="848" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A848" t="s">
         <v>973</v>
       </c>
@@ -44277,8 +47160,15 @@
       <c r="P848" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="849" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q848">
+        <v>2</v>
+      </c>
+      <c r="S848" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="849" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A849" t="s">
         <v>973</v>
       </c>
@@ -44321,8 +47211,15 @@
       <c r="P849" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="850" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q849">
+        <v>2</v>
+      </c>
+      <c r="S849" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="850" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A850" t="s">
         <v>973</v>
       </c>
@@ -44365,8 +47262,15 @@
       <c r="P850" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="851" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q850">
+        <v>2</v>
+      </c>
+      <c r="S850" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="851" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A851" t="s">
         <v>973</v>
       </c>
@@ -44409,8 +47313,15 @@
       <c r="P851" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="852" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q851">
+        <v>2</v>
+      </c>
+      <c r="S851" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="852" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A852" t="s">
         <v>973</v>
       </c>
@@ -44453,8 +47364,15 @@
       <c r="P852" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="853" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q852">
+        <v>0</v>
+      </c>
+      <c r="S852" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="853" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A853" t="s">
         <v>973</v>
       </c>
@@ -44497,8 +47415,15 @@
       <c r="P853" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="854" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q853">
+        <v>2</v>
+      </c>
+      <c r="S853" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="854" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A854" t="s">
         <v>973</v>
       </c>
@@ -44541,8 +47466,15 @@
       <c r="P854" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="855" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q854">
+        <v>1</v>
+      </c>
+      <c r="S854" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="855" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A855" t="s">
         <v>973</v>
       </c>
@@ -44585,8 +47517,15 @@
       <c r="P855" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="856" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q855">
+        <v>2</v>
+      </c>
+      <c r="S855" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="856" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A856" t="s">
         <v>978</v>
       </c>
@@ -44629,8 +47568,15 @@
       <c r="P856" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="857" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q856">
+        <v>2</v>
+      </c>
+      <c r="S856" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="857" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A857" t="s">
         <v>978</v>
       </c>
@@ -44673,8 +47619,15 @@
       <c r="P857" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="858" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q857">
+        <v>1</v>
+      </c>
+      <c r="S857" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="858" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A858" t="s">
         <v>978</v>
       </c>
@@ -44717,8 +47670,15 @@
       <c r="P858" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="859" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q858">
+        <v>1</v>
+      </c>
+      <c r="S858" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="859" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A859" t="s">
         <v>978</v>
       </c>
@@ -44767,8 +47727,15 @@
       <c r="P859" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="860" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q859">
+        <v>2</v>
+      </c>
+      <c r="S859" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="860" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A860" t="s">
         <v>978</v>
       </c>
@@ -44817,8 +47784,15 @@
       <c r="P860" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="861" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q860">
+        <v>2</v>
+      </c>
+      <c r="S860" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="861" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A861" t="s">
         <v>978</v>
       </c>
@@ -44867,8 +47841,15 @@
       <c r="P861" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="862" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q861">
+        <v>2</v>
+      </c>
+      <c r="S861" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="862" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A862" t="s">
         <v>978</v>
       </c>
@@ -44911,8 +47892,15 @@
       <c r="P862" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="863" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q862">
+        <v>0</v>
+      </c>
+      <c r="S862" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="863" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A863" t="s">
         <v>978</v>
       </c>
@@ -44955,8 +47943,15 @@
       <c r="P863" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="864" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q863">
+        <v>1</v>
+      </c>
+      <c r="S863" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="864" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A864" t="s">
         <v>978</v>
       </c>
@@ -44999,8 +47994,15 @@
       <c r="P864" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="865" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q864">
+        <v>1</v>
+      </c>
+      <c r="S864" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="865" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A865" t="s">
         <v>978</v>
       </c>
@@ -45043,8 +48045,15 @@
       <c r="P865" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="866" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q865">
+        <v>1</v>
+      </c>
+      <c r="S865" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="866" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A866" t="s">
         <v>978</v>
       </c>
@@ -45087,8 +48096,15 @@
       <c r="P866" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="867" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q866">
+        <v>2</v>
+      </c>
+      <c r="S866" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="867" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A867" t="s">
         <v>978</v>
       </c>
@@ -45131,8 +48147,15 @@
       <c r="P867" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="868" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q867">
+        <v>1</v>
+      </c>
+      <c r="S867" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="868" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A868" t="s">
         <v>978</v>
       </c>
@@ -45175,8 +48198,15 @@
       <c r="P868" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="869" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q868">
+        <v>1</v>
+      </c>
+      <c r="S868" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="869" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A869" t="s">
         <v>978</v>
       </c>
@@ -45219,8 +48249,15 @@
       <c r="P869" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="870" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q869">
+        <v>2</v>
+      </c>
+      <c r="S869" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="870" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A870" t="s">
         <v>978</v>
       </c>
@@ -45263,8 +48300,15 @@
       <c r="P870" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="871" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q870">
+        <v>0</v>
+      </c>
+      <c r="S870" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="871" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A871" t="s">
         <v>978</v>
       </c>
@@ -45307,8 +48351,15 @@
       <c r="P871" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="872" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q871">
+        <v>2</v>
+      </c>
+      <c r="S871" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="872" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A872" t="s">
         <v>978</v>
       </c>
@@ -45351,8 +48402,15 @@
       <c r="P872" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="873" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q872">
+        <v>1</v>
+      </c>
+      <c r="S872" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="873" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A873" t="s">
         <v>991</v>
       </c>
@@ -45395,8 +48453,15 @@
       <c r="P873" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="874" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q873">
+        <v>2</v>
+      </c>
+      <c r="S873" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="874" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A874" t="s">
         <v>991</v>
       </c>
@@ -45439,8 +48504,15 @@
       <c r="P874" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="875" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q874">
+        <v>1</v>
+      </c>
+      <c r="S874" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="875" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A875" t="s">
         <v>991</v>
       </c>
@@ -45483,8 +48555,15 @@
       <c r="P875" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="876" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q875">
+        <v>1</v>
+      </c>
+      <c r="S875" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="876" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A876" t="s">
         <v>991</v>
       </c>
@@ -45527,8 +48606,15 @@
       <c r="P876" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="877" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q876">
+        <v>1</v>
+      </c>
+      <c r="S876" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="877" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A877" t="s">
         <v>991</v>
       </c>
@@ -45571,8 +48657,15 @@
       <c r="P877" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="878" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q877">
+        <v>1</v>
+      </c>
+      <c r="S877" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="878" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A878" t="s">
         <v>991</v>
       </c>
@@ -45621,8 +48714,15 @@
       <c r="P878" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="879" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q878">
+        <v>2</v>
+      </c>
+      <c r="S878" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="879" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A879" t="s">
         <v>991</v>
       </c>
@@ -45665,8 +48765,15 @@
       <c r="P879" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="880" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q879">
+        <v>1</v>
+      </c>
+      <c r="S879" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="880" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A880" t="s">
         <v>991</v>
       </c>
@@ -45709,8 +48816,15 @@
       <c r="P880" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="881" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q880">
+        <v>0</v>
+      </c>
+      <c r="S880" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="881" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A881" t="s">
         <v>991</v>
       </c>
@@ -45753,8 +48867,15 @@
       <c r="P881" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="882" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q881">
+        <v>2</v>
+      </c>
+      <c r="S881" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="882" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A882" t="s">
         <v>991</v>
       </c>
@@ -45797,8 +48918,15 @@
       <c r="P882" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="883" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q882">
+        <v>0</v>
+      </c>
+      <c r="S882" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="883" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A883" t="s">
         <v>991</v>
       </c>
@@ -45841,8 +48969,15 @@
       <c r="P883" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="884" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q883">
+        <v>2</v>
+      </c>
+      <c r="S883" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="884" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A884" t="s">
         <v>991</v>
       </c>
@@ -45885,8 +49020,15 @@
       <c r="P884" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="885" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q884">
+        <v>1</v>
+      </c>
+      <c r="S884" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="885" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A885" t="s">
         <v>991</v>
       </c>
@@ -45929,8 +49071,15 @@
       <c r="P885" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="886" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q885">
+        <v>1</v>
+      </c>
+      <c r="S885" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="886" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A886" t="s">
         <v>991</v>
       </c>
@@ -45973,8 +49122,15 @@
       <c r="P886" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="887" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q886">
+        <v>1</v>
+      </c>
+      <c r="S886" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="887" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A887" t="s">
         <v>991</v>
       </c>
@@ -46017,8 +49173,15 @@
       <c r="P887" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="888" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q887">
+        <v>2</v>
+      </c>
+      <c r="S887" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="888" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A888" t="s">
         <v>991</v>
       </c>
@@ -46061,8 +49224,15 @@
       <c r="P888" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="889" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q888">
+        <v>2</v>
+      </c>
+      <c r="S888" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="889" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A889" t="s">
         <v>991</v>
       </c>
@@ -46105,8 +49275,15 @@
       <c r="P889" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="890" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q889">
+        <v>1</v>
+      </c>
+      <c r="S889" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="890" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A890" t="s">
         <v>991</v>
       </c>
@@ -46149,8 +49326,15 @@
       <c r="P890" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="891" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q890">
+        <v>2</v>
+      </c>
+      <c r="S890" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="891" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A891" t="s">
         <v>991</v>
       </c>
@@ -46193,8 +49377,15 @@
       <c r="P891" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="892" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q891">
+        <v>1</v>
+      </c>
+      <c r="S891" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="892" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A892" t="s">
         <v>1000</v>
       </c>
@@ -46243,8 +49434,15 @@
       <c r="P892" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="893" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q892">
+        <v>2</v>
+      </c>
+      <c r="S892" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="893" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A893" t="s">
         <v>1000</v>
       </c>
@@ -46287,8 +49485,15 @@
       <c r="P893" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="894" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q893">
+        <v>2</v>
+      </c>
+      <c r="S893" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="894" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A894" t="s">
         <v>1000</v>
       </c>
@@ -46331,8 +49536,15 @@
       <c r="P894" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="895" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q894">
+        <v>2</v>
+      </c>
+      <c r="S894" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="895" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A895" t="s">
         <v>1000</v>
       </c>
@@ -46381,8 +49593,15 @@
       <c r="P895" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="896" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q895">
+        <v>2</v>
+      </c>
+      <c r="S895" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="896" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A896" t="s">
         <v>1000</v>
       </c>
@@ -46431,8 +49650,15 @@
       <c r="P896" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="897" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q896">
+        <v>2</v>
+      </c>
+      <c r="S896" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="897" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A897" t="s">
         <v>1000</v>
       </c>
@@ -46475,8 +49701,15 @@
       <c r="P897" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="898" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q897">
+        <v>1</v>
+      </c>
+      <c r="S897" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="898" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A898" t="s">
         <v>1000</v>
       </c>
@@ -46519,8 +49752,15 @@
       <c r="P898" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="899" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q898">
+        <v>2</v>
+      </c>
+      <c r="S898" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="899" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A899" t="s">
         <v>1000</v>
       </c>
@@ -46563,8 +49803,15 @@
       <c r="P899" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="900" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q899">
+        <v>2</v>
+      </c>
+      <c r="S899" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="900" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A900" t="s">
         <v>1000</v>
       </c>
@@ -46607,8 +49854,15 @@
       <c r="P900" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="901" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q900">
+        <v>1</v>
+      </c>
+      <c r="S900" t="str">
+        <f t="shared" si="0"/>
+        <v>Phù hợp 1 phần</v>
+      </c>
+    </row>
+    <row r="901" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A901" t="s">
         <v>1000</v>
       </c>
@@ -46651,8 +49905,15 @@
       <c r="P901" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="902" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q901">
+        <v>2</v>
+      </c>
+      <c r="S901" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="902" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A902" t="s">
         <v>1000</v>
       </c>
@@ -46695,8 +49956,15 @@
       <c r="P902" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="903" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q902">
+        <v>2</v>
+      </c>
+      <c r="S902" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="903" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A903" t="s">
         <v>1000</v>
       </c>
@@ -46739,8 +50007,15 @@
       <c r="P903" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="904" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q903">
+        <v>0</v>
+      </c>
+      <c r="S903" t="str">
+        <f t="shared" si="0"/>
+        <v>ko hợp</v>
+      </c>
+    </row>
+    <row r="904" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A904" t="s">
         <v>1000</v>
       </c>
@@ -46783,8 +50058,15 @@
       <c r="P904" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="905" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q904">
+        <v>2</v>
+      </c>
+      <c r="S904" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="905" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A905" t="s">
         <v>1000</v>
       </c>
@@ -46827,8 +50109,15 @@
       <c r="P905" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="906" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q905">
+        <v>2</v>
+      </c>
+      <c r="S905" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="906" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A906" t="s">
         <v>1000</v>
       </c>
@@ -46877,8 +50166,15 @@
       <c r="P906" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="907" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q906">
+        <v>2</v>
+      </c>
+      <c r="S906" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="907" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A907" t="s">
         <v>1000</v>
       </c>
@@ -46921,8 +50217,15 @@
       <c r="P907" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="908" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+      <c r="Q907">
+        <v>2</v>
+      </c>
+      <c r="S907" t="str">
+        <f t="shared" si="0"/>
+        <v>ok</v>
+      </c>
+    </row>
+    <row r="908" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A908" t="s">
         <v>1010</v>
       </c>
@@ -46966,7 +50269,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="909" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="909" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A909" t="s">
         <v>1010</v>
       </c>
@@ -47010,7 +50313,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="910" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="910" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A910" t="s">
         <v>1010</v>
       </c>
@@ -47054,7 +50357,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="911" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="911" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A911" t="s">
         <v>1010</v>
       </c>
@@ -47098,7 +50401,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="912" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
+    <row r="912" spans="1:19" hidden="1" x14ac:dyDescent="0.3">
       <c r="A912" t="s">
         <v>1010</v>
       </c>
@@ -87389,7 +90692,7 @@
   <autoFilter ref="A1:A1814" xr:uid="{00000000-0001-0000-0000-000000000000}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Q021"/>
+        <filter val="Q050"/>
       </filters>
     </filterColumn>
   </autoFilter>
